--- a/data/증권뉴스_2025-11-03.xlsx
+++ b/data/증권뉴스_2025-11-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>코스피, 2% 넘게 올라 사상 최고치…4200선 눈앞</t>
+          <t>큰손 개미의 귀환 '코스피 불장' 원인?…달라붙은 종목은</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>코스피지수가 3일 장중 2% 넘게 상승폭을 확대해 사상 처음으로 4190선을 넘어섰다. 아시아태평양경제협력체(APEC) 회의를 계기로 ..</t>
+          <t>코스피가 사상 처음 4,000선을 돌파한 이후 랠리를 이어가자, 거액을 운용하는 개인투자자들의 주식시장 참여가 크게 늘어난 것으로 나타..</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-11-03 11:18:19</t>
+          <t>2025-11-03 11:30:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005206018</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087399</t>
         </is>
       </c>
     </row>
@@ -491,27 +491,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"20% 더 오른다"…개미들 반년간 '폭풍매수' 나선 종목</t>
+          <t>‘불장’코스피…반도체·2차전지 섹터만 랠리</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>네이버와 카카오가 하반기 들어 오름폭을 확대하고 있다. 인공지능(AI) 사업 성장과 실적 개선 기대가 커지면서 매수세가 유입되고 있다...</t>
+          <t>KRX 35개 지수 중 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 지난 한 달간 코스피가..</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-11-03 11:14:14</t>
+          <t>2025-11-03 11:22:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005206017</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551685</t>
         </is>
       </c>
     </row>
@@ -521,27 +521,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>“지금도 안 늦었을까요?”…‘50만닉스’ 불과 열흘 만에 ‘60만닉스’ 돌파 [종목Pick]</t>
+          <t>초고수, 잇단 목표주가 상승에 SK하이닉스 매수 [주식 초고수는 지금]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“이미 엄청난 속도로 올랐지만 SK하이닉스 주가는 더 오를 것이란 사람들이 많던데요. 지금 투자하는 건 늦지 않은 걸까요?”(직장인 A..</t>
+          <t>日노무라, SK하닉 목표주가 84만원 제시 SK증권서는 목표주가 100만원으로 상향 네이버, 레인보우로보틱스도 순매수 호재 이어졌던 현..</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-11-03 11:10:19</t>
+          <t>2025-11-03 11:21:14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551645</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583517</t>
         </is>
       </c>
     </row>
@@ -551,27 +551,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>‘서로 밥도 안 먹던’ 상업·한일은행 동우회 26년 만에 통합</t>
+          <t>코스피, 2% 넘게 올라 사상 최고치…4200선 눈앞</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>‘우리은행 동우회’로 통합 출범, 고질적 계파 문화 사라질까 주목 1999년 한일은행과 상업은행이 통합해 출범한 우리은행이 26년 만에..</t>
+          <t>코스피지수가 3일 장중 2% 넘게 상승폭을 확대해 사상 처음으로 4190선을 넘어섰다. 아시아태평양경제협력체(APEC) 회의를 계기로 ..</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-11-03 11:08:26</t>
+          <t>2025-11-03 11:18:19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003938571</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005206018</t>
         </is>
       </c>
     </row>
@@ -581,27 +581,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>꼼수 막아야지... 자사주 소각 의무화 대상에 신탁 통한 간접 취득도 포함</t>
+          <t>"20% 더 오른다"…개미들 반년간 2.7조 '폭풍매수' 나선 종목</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>정부와 여당이 ‘자사주 의무 소각’을 골자로 한 3차 상법 개정안을 추진 중인 가운데, 신탁 계약을 통해 간접 취득한 자사주도 소각 대..</t>
+          <t>네이버와 카카오가 하반기 들어 오름폭을 확대하고 있다. 인공지능(AI) 사업 성장과 실적 개선 기대가 커지면서 매수세가 유입되고 있다...</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-11-03 11:01:19</t>
+          <t>2025-11-03 11:14:14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119648</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005206017</t>
         </is>
       </c>
     </row>
@@ -611,27 +611,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"효성중공업, 목표주가 300만원" 100% 상향... 현대차, 美하이브리드시장 진격 [株토피아]</t>
+          <t>“지금도 안 늦었을까요?”…‘50만닉스’ 열흘 만 ‘60만닉스’ 돌파에 ‘100만닉스’ 목표가까지 [종목Pick]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11월 3일 오전, 주요 증권사 리포트를 정리해드립니다. 삼성물산은 원전·바이오 등 신성장동력에 더해 지배구조 개선 기대감이 반영되며 ..</t>
+          <t>“이미 엄청난 속도로 올랐지만 SK하이닉스 주가는 더 오를 것이란 사람들이 많던데요. 지금 투자하는 건 늦지 않은 걸까요?”(직장인 A..</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>파이낸셜뉴스</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-11-03 11:01:16</t>
+          <t>2025-11-03 11:10:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005428584</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551645</t>
         </is>
       </c>
     </row>
@@ -641,27 +641,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엔비디아 GPU 5만장씩 'AI동맹'…'60만닉스' 탄생 '11만전자' 눈앞</t>
+          <t>‘서로 밥도 안 먹던’ 상업·한일은행 동우회 26년 만에 통합</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>코스피가 장중 사상 최고치를 잇달아 경신하고 있다. SK하이닉스는 엔비디아발 AI(인공지능) 훈풍으로 주당 60만원에 거래되기도 했다...</t>
+          <t>‘우리은행 동우회’로 통합 출범, 고질적 계파 문화 사라질까 주목 1999년 한일은행과 상업은행이 통합해 출범한 우리은행이 26년 만에..</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-11-03 10:56:36</t>
+          <t>2025-11-03 11:08:26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272407</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003938571</t>
         </is>
       </c>
     </row>
@@ -671,27 +671,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'10만전자·60만닉스' 랠리…홍콩 레버리지 ETF로 돈 몰린다</t>
+          <t>꼼수 막아야지... 자사주 소각 의무화 대상에 신탁 통한 간접 취득도 포함</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>삼성전자와 SK하이닉스가 나란히 사상 최고가를 경신하며 고공행진을 이어가는 가운데, 이들 종목을 기초자산으로 한 해외 레버리지 상장지수..</t>
+          <t>정부와 여당이 ‘자사주 의무 소각’을 골자로 한 3차 상법 개정안을 추진 중인 가운데, 신탁 계약을 통해 간접 취득한 자사주도 소각 대..</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-11-03 10:54:44</t>
+          <t>2025-11-03 11:01:19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013576788</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119648</t>
         </is>
       </c>
     </row>
@@ -701,27 +701,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>사상 최초 ‘60만닉스’ 터치…‘엔비디아 동맹’ 韓 AI 대표주 ‘불기둥’ [투자360]</t>
+          <t>"효성중공업, 목표주가 300만원" 100% 상향... 현대차, 美하이브리드시장 진격 [株토피아]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>이재명 대통령이 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자 접견에 앞서 국내 기업 대표들과 함께 기..</t>
+          <t>11월 3일 오전, 주요 증권사 리포트를 정리해드립니다. 삼성물산은 원전·바이오 등 신성장동력에 더해 지배구조 개선 기대감이 반영되며 ..</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11-03 10:46:19</t>
+          <t>2025-11-03 11:01:16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551595</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005428584</t>
         </is>
       </c>
     </row>
@@ -731,27 +731,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"젠슨 황 엔비디아 CEO, 10억달러 자사주 현금화"</t>
+          <t>엔비디아 GPU 5만장씩 'AI동맹'…'60만닉스' 탄생 '11만전자' 눈앞</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인공지능(AI) 붐과 함께 승승장구 중인 엔비디아의 젠슨 황 최고경영자(CEO)가 지난 6월 이후 10억달러가 넘는 자사주를 현금화했다..</t>
+          <t>코스피가 장중 사상 최고치를 잇달아 경신하고 있다. SK하이닉스는 엔비디아발 AI(인공지능) 훈풍으로 주당 60만원에 거래되기도 했다...</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-11-03 10:42:25</t>
+          <t>2025-11-03 10:56:36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673522</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272407</t>
         </is>
       </c>
     </row>
@@ -761,27 +761,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사상 초유의 60만닉스 탄생…SK하닉 장중 7%대 급등[줍줍리포트]</t>
+          <t>'10만전자·60만닉스' 랠리…홍콩 레버리지 ETF로 돈 몰린다</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가가 장 중 7% 넘게 상승하며 60만 원 돌파에 성공했다. 3일 한국거래소에 따르면 이날 오전 10시 23분 현재 SK..</t>
+          <t>삼성전자와 SK하이닉스가 나란히 사상 최고가를 경신하며 고공행진을 이어가는 가운데, 이들 종목을 기초자산으로 한 해외 레버리지 상장지수..</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-11-03 10:35:10</t>
+          <t>2025-11-03 10:54:44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551133</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013576788</t>
         </is>
       </c>
     </row>
@@ -791,27 +791,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>367조 '토큰증권'시장 정조준… '조각투자' 플랫폼 최종선정 관건은</t>
+          <t>사상 최초 ‘60만닉스’ 터치…‘엔비디아 동맹’ 韓 AI 대표주 ‘불기둥’ [투자360]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2030년 최대 367조원 규모의 시장으로 평가 받는 미래 토큰증권(STO) 시장 선점을 위한 조각투자 장외거래소(유통플랫폼) 예비인가..</t>
+          <t>이재명 대통령이 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자 접견에 앞서 국내 기업 대표들과 함께 기..</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-11-03 10:21:49</t>
+          <t>2025-11-03 10:46:19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110803</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551595</t>
         </is>
       </c>
     </row>
@@ -821,27 +821,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>현대오토에버 ‘엔비디아 AI 동맹’ 수혜 기대에 급등 [종목Pick]</t>
+          <t>"젠슨 황 엔비디아 CEO, 10억달러 자사주 현금화"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>이재명 대통령이 지난달 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자(CEO) 접견 전 과학기술정보통신..</t>
+          <t>인공지능(AI) 붐과 함께 승승장구 중인 엔비디아의 젠슨 황 최고경영자(CEO)가 지난 6월 이후 10억달러가 넘는 자사주를 현금화했다..</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-11-03 10:19:10</t>
+          <t>2025-11-03 10:42:25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551565</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673522</t>
         </is>
       </c>
     </row>
@@ -851,27 +851,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>“시진핑 만나 기뻐” 박진영 소감에 한한령 해제 기대 ‘솔솔’…JYP 엔터 5%대 상승 [종목Pick]</t>
+          <t>사상 초유의 60만닉스 탄생…SK하닉 장중 7%대 급등[줍줍리포트]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JYP 엔터테인먼트 5.44% 오름세 기록 와이지엔터테인먼트 +0.66%·하이브 +0.29% 박 위원장 “양국 국민 더 가까워졌으면” ..</t>
+          <t>SK하이닉스 주가가 장 중 7% 넘게 상승하며 60만 원 돌파에 성공했다. 3일 한국거래소에 따르면 이날 오전 10시 23분 현재 SK..</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-11-03 10:17:15</t>
+          <t>2025-11-03 10:35:10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551564</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551133</t>
         </is>
       </c>
     </row>
@@ -881,27 +881,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>광동제약 EB 철회 불똥...태광산업, 자사주 EB 고심</t>
+          <t>367조 '토큰증권'시장 정조준… '조각투자' 플랫폼 최종선정 관건은</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>광동제약의 자기주식 교환사채 발행 철회 불똥이 태광산업으로 번졌다. 태광산업의 자사주 EB 발행 규모가 발행주식총수의 24%에 달하는 ..</t>
+          <t>2030년 최대 367조원 규모의 시장으로 평가 받는 미래 토큰증권(STO) 시장 선점을 위한 조각투자 장외거래소(유통플랫폼) 예비인가..</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>아이뉴스24</t>
+          <t>머니S</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-11-03 10:14:11</t>
+          <t>2025-11-03 10:21:49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0000977292</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001110803</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>“삼전 수익률보다 높다”…‘15만전자·75만닉스’ 기대에 반도체 ETF로 몰리는 개미들 [투자360]</t>
+          <t>현대오토에버 ‘엔비디아 AI 동맹’ 수혜 기대에 급등 [종목Pick]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인 투자자 반도체 랠리 ‘확신 베팅’ 증권가도 삼전·SK하이닉스 목표주가 상향 일부 반도체 ETF, 개별종목 한달 수익률 추월 4분기..</t>
+          <t>이재명 대통령이 지난달 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자(CEO) 접견 전 과학기술정보통신..</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-03 10:01:09</t>
+          <t>2025-11-03 10:19:10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551534</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551565</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>현대차, 한달새 시총 15조 늘자 순위도 3계단 껑충…‘개미 랠리’ 속 목표가 36만원 등장 [투자360]</t>
+          <t>“시진핑 만나 기뻐” 박진영 소감에 한한령 해제 기대 ‘솔솔’…JYP 엔터 5%대 상승 [종목Pick]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>현대차, 한달새 시총 15조↑…한 달간 개인 1조4000억·기관 800억 순매수 거래대금 23배 폭증·신용비율 0.45까지 상승…‘개미..</t>
+          <t>JYP 엔터테인먼트 5.44% 오름세 기록 와이지엔터테인먼트 +0.66%·하이브 +0.29% 박 위원장 “양국 국민 더 가까워졌으면” ..</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-03 09:54:09</t>
+          <t>2025-11-03 10:17:15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551522</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551564</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>‘연말 랠리’ 기대 꺾인 뉴욕증시…소비 둔화·셧다운·연준 경계 삼중 악재 [투자360]</t>
+          <t>광동제약 EB 철회 불똥...태광산업, 자사주 EB 고심</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1950년 이후 11월 평균 수익률 1.82%, 12월 1.49% ‘강세 구간’ 올해는 소비 5.3% 감소·셧다운 장기화로 연말 소비 ..</t>
+          <t>광동제약의 자기주식 교환사채 발행 철회 불똥이 태광산업으로 번졌다. 태광산업의 자사주 EB 발행 규모가 발행주식총수의 24%에 달하는 ..</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>아이뉴스24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-03 09:51:15</t>
+          <t>2025-11-03 10:14:11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551518</t>
+          <t>https://n.news.naver.com/mnews/article/031/0000977292</t>
         </is>
       </c>
     </row>
@@ -1001,27 +1001,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'월요병'이 낫네…코스피, 개인 7000억 순매수에 4160선까지 치솟아[마켓시그널]</t>
+          <t>“삼전 수익률보다 높다”…‘15만전자·75만닉스’ 기대에 반도체 ETF로 몰리는 개미들 [투자360]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>코스피 지수가 전인미답의 ‘사천피’ 달성 이후에도 숨 고르기 장세 없이 고공 행진 중이다. 상장 기업들의 실적 발표를 앞두고 호실적이 ..</t>
+          <t>개인 투자자 반도체 랠리 ‘확신 베팅’ 증권가도 삼전·SK하이닉스 목표주가 상향 일부 반도체 ETF, 개별종목 한달 수익률 추월 4분기..</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-03 09:48:10</t>
+          <t>2025-11-03 10:01:09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551090</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551534</t>
         </is>
       </c>
     </row>
@@ -1031,27 +1031,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"4150선 돌파"…코스피, 개인 '사자'에 사상 최고치 또 경신</t>
+          <t>현대차, 한달새 시총 15조 늘자 순위도 3계단 껑충…‘개미 랠리’ 속 목표가 36만원 등장 [투자360]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>원·달러 환율 3.8원 오른 1428.2원 코스피가 개인들의 매수세에 힘입어 상승 출발하면서 또다시 사상 최고치를 경신했다. 3일 한국..</t>
+          <t>현대차, 한달새 시총 15조↑…한 달간 개인 1조4000억·기관 800억 순매수 거래대금 23배 폭증·신용비율 0.45까지 상승…‘개미..</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>더팩트</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-03 09:44:17</t>
+          <t>2025-11-03 09:54:09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000439809</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551522</t>
         </is>
       </c>
     </row>
@@ -1061,27 +1061,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>두나무·빗썸에 ‘금융사’ 잣대 들이댄 공정위 vs 금융위 “가상자산은 금융 아냐”</t>
+          <t>‘연말 랠리’ 기대 꺾인 뉴욕증시…소비 둔화·셧다운·연준 경계 삼중 악재 [투자360]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>공정위 ‘두나무·빗썸 금융복합그룹 지정’ 추진 ‘금가분리’ 원칙과 정면충돌…정책 딜레마 주력사업은 ‘비금융’, 그룹은 ‘금융’(?) 법..</t>
+          <t>1950년 이후 11월 평균 수익률 1.82%, 12월 1.49% ‘강세 구간’ 올해는 소비 5.3% 감소·셧다운 장기화로 연말 소비 ..</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-03 09:42:05</t>
+          <t>2025-11-03 09:51:15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583414</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551518</t>
         </is>
       </c>
     </row>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"中, 미 조선·해운 보복 철회"…한화오션 3%대 강세</t>
+          <t>'월요병'이 낫네…코스피, 개인 7000억 순매수에 4160선까지 치솟아[마켓시그널]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화오션 주가가 3일 장 초반 강세다. 중국이 한화오션의 미국 자회사에 부과한 제재가 풀릴 가능성이 제기되면서다. 이날 오전 9시27분..</t>
+          <t>코스피 지수가 전인미답의 ‘사천피’ 달성 이후에도 숨 고르기 장세 없이 고공 행진 중이다. 상장 기업들의 실적 발표를 앞두고 호실적이 ..</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-03 09:39:14</t>
+          <t>2025-11-03 09:48:10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205931</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551090</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>증권가 "내년엔 '오천피' 간다…정상화 넘어 '코리아프리미엄' 국면 진입"</t>
+          <t>"4150선 돌파"…코스피, 개인 '사자'에 사상 최고치 또 경신</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>국내 증권사들이 내년 코스피 지수 상단을 최고 5000포인트까지 줄줄이 상향했다. 코리아디스카운트 해소를 넘어 프리미엄 국면에 진입할 ..</t>
+          <t>원·달러 환율 3.8원 오른 1428.2원 코스피가 개인들의 매수세에 힘입어 상승 출발하면서 또다시 사상 최고치를 경신했다. 3일 한국..</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>더팩트</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-03 09:34:13</t>
+          <t>2025-11-03 09:44:17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580759</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000439809</t>
         </is>
       </c>
     </row>
@@ -1151,27 +1151,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>반도체·2차전지 빼고 전부 ‘왕따’…코스피 상승률 못 따라가는 KRX 업종 지수 [투자360]</t>
+          <t>두나무·빗썸에 ‘금융사’ 잣대 들이댄 공정위 vs 금융위 “가상자산은 금융 아냐”</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KRX 35개 지수 가운데 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 [챗GPT를 사용해..</t>
+          <t>공정위 ‘두나무·빗썸 금융복합그룹 지정’ 추진 ‘금가분리’ 원칙과 정면충돌…정책 딜레마 주력사업은 ‘비금융’, 그룹은 ‘금융’(?) 법..</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-03 09:31:12</t>
+          <t>2025-11-03 09:42:05</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551479</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583414</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스테이블코인, '외국환'으로 묶이나… 규제냐 제도권 편입이냐 기로에 선 시장</t>
+          <t>"中, 미 조선·해운 보복 철회"…한화오션 3%대 강세</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>스테이블코인을 '외국환'으로 규제하려는 입법 논의가 본격화하면서, 그 법적 지위를 둘러싼 논쟁이 국내 디지털 금융 정책의 핵심 변수로 ..</t>
+          <t>한화오션 주가가 3일 장 초반 강세다. 중국이 한화오션의 미국 자회사에 부과한 제재가 풀릴 가능성이 제기되면서다. 이날 오전 9시27분..</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-03 09:30:09</t>
+          <t>2025-11-03 09:39:14</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087382</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205931</t>
         </is>
       </c>
     </row>
@@ -1211,27 +1211,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>숨고르기 없는 코스피…'4200피' 향해 질주</t>
+          <t>증권가 "내년엔 '오천피' 간다…정상화 넘어 '코리아프리미엄' 국면 진입"</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>역사상 최고치를 연일 갱신 중인 코스피가 ‘4200선’을 향해 달려가고 있다. 코스피가 상승 출발해 4130대를 나타낸 3일 오전 서울..</t>
+          <t>국내 증권사들이 내년 코스피 지수 상단을 최고 5000포인트까지 줄줄이 상향했다. 코리아디스카운트 해소를 넘어 프리미엄 국면에 진입할 ..</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-11-03 09:22:14</t>
+          <t>2025-11-03 09:34:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154477</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580759</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1241,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>코스피, 4200 등반 시도…HD현대중공업·한화오션 3%대 강세</t>
+          <t>반도체·2차전지 빼고 전부 ‘왕따’…코스피 상승률 못 따라가는 KRX 업종 지수 [투자360]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>지난주 ‘슈퍼위크’를 소화한 코스피가 3일 또 한번 강세로 장을 시작했다. 한국거래소에 따르면 코스피는 전장보다 15.86포인트(0.3..</t>
+          <t>KRX 35개 지수 가운데 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 [챗GPT를 사용해..</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11-03 09:13:22</t>
+          <t>2025-11-03 09:31:12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991048</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551479</t>
         </is>
       </c>
     </row>
@@ -1271,27 +1271,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코스피, 장중 또 사상 최고치 경신…4160선 위로</t>
+          <t>스테이블코인, '외국환'으로 묶이나… 규제냐 제도권 편입이냐 기로에 선 시장</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>코스피지수가 3일 장 초반 1% 넘게 올라 장중 기준 사상 최고치를 재차 경신했다. 엔비디아가 한국 정부와 기업에 인공지능(AI) 칩 ..</t>
+          <t>스테이블코인을 '외국환'으로 규제하려는 입법 논의가 본격화하면서, 그 법적 지위를 둘러싼 논쟁이 국내 디지털 금융 정책의 핵심 변수로 ..</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-11-03 09:11:12</t>
+          <t>2025-11-03 09:30:09</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205888</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087382</t>
         </is>
       </c>
     </row>
@@ -1301,27 +1301,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코스피 4150선도 돌파…코스닥도 상승 출발</t>
+          <t>숨고르기 없는 코스피…'4200피' 향해 질주</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>코스피 지수가 3일 사상 최고치를 다시 경신하며 출발했다. 이날 오전 9시 16분 기준 코스피 지수는 전 거래일 대비 48.74포인트(..</t>
+          <t>역사상 최고치를 연일 갱신 중인 코스피가 ‘4200선’을 향해 달려가고 있다. 코스피가 상승 출발해 4130대를 나타낸 3일 오전 서울..</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-11-03 09:03:08</t>
+          <t>2025-11-03 09:22:14</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119582</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154477</t>
         </is>
       </c>
     </row>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LG화학, 업황개선·LG엔솔 지분활용 주목…목표가 35%↑</t>
+          <t>코스피, 4200 등반 시도…HD현대중공업·한화오션 3%대 강세</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>iM증권이 3일 LG화학에 대한 목표주가를 기존 대비 35% 높은 50만원으로 상향했다. 내년 업황 회복과 LG에너지솔루션 지분활용 의..</t>
+          <t>지난주 ‘슈퍼위크’를 소화한 코스피가 3일 또 한번 강세로 장을 시작했다. 한국거래소에 따르면 코스피는 전장보다 15.86포인트(0.3..</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>디지털타임스</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:23</t>
+          <t>2025-11-03 09:13:22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272276</t>
+          <t>https://n.news.naver.com/mnews/article/029/0002991048</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>"사모펀드 규제? 국내 자본시장 죽일 것"</t>
+          <t>코스피, 장중 또 사상 최고치 경신…4160선 위로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MBK파트너스의 홈플러스 사태를 계기로 정치권과 금융당국 내부에서 사모펀드(PE)의 기업 지배권 관련 규제가 필요하다는 목소리가 커지고..</t>
+          <t>코스피지수가 3일 장 초반 1% 넘게 올라 장중 기준 사상 최고치를 재차 경신했다. 엔비디아가 한국 정부와 기업에 인공지능(AI) 칩 ..</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:09</t>
+          <t>2025-11-03 09:11:12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087377</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205888</t>
         </is>
       </c>
     </row>
@@ -1391,27 +1391,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETF 배당금도 분리과세 될까...관건은 '배당성향' 요건</t>
+          <t>코스피 4150선도 돌파…코스닥도 상승 출발</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>고배당주에 투자하는 ETF 분배금(배당금)은 왜 분리과세 안 해주나요" 배당소득의 분리과세방안이 국회에서 논의중인 가운데 고배당 기업들..</t>
+          <t>코스피 지수가 3일 사상 최고치를 다시 경신하며 출발했다. 이날 오전 9시 16분 기준 코스피 지수는 전 거래일 대비 48.74포인트(..</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:09</t>
+          <t>2025-11-03 09:03:08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041354</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119582</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>내 속만 타들어 가네…코스피 불 뿜는데 '코스닥 3000 시대' 언제 오나</t>
+          <t>LG화학, 업황개선·LG엔솔 지분활용 주목…목표가 35%↑</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
+          <t>iM증권이 3일 LG화학에 대한 목표주가를 기존 대비 35% 높은 50만원으로 상향했다. 내년 업황 회복과 LG에너지솔루션 지분활용 의..</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:00</t>
+          <t>2025-11-03 09:00:23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272275</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272276</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>성장축 올라탄 종목은 따로 있다… 네 전문가가 밝힌 ‘현재 최우선 체크 종목’[진짜 주식 3부]</t>
+          <t>"사모펀드 규제? 국내 자본시장 죽일 것"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>지난 10월 31일(금) 방송된 한국경제TV ‘진짜 주식 3부’에서는 신학수 전문가(MJ스탁), 한중연 전문가(에스엠티엠 컨설팅), 전..</t>
+          <t>MBK파트너스의 홈플러스 사태를 계기로 정치권과 금융당국 내부에서 사모펀드(PE)의 기업 지배권 관련 규제가 필요하다는 목소리가 커지고..</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-11-03 08:56:10</t>
+          <t>2025-11-03 09:00:09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229280</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087377</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>“순금에 이자가 붙는다고?”…‘하나골드신탁’ 연일 매진</t>
+          <t>ETF 배당금도 분리과세 될까...관건은 '배당성향' 요건</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>‘장롱금’ 140조 깨운다 ‘금 신탁’, 90분만에 40억 ‘완판’ 순금 100g 이상 맡기면 1.5% 이자 고액 자산가 증여 수단으로..</t>
+          <t>고배당주에 투자하는 ETF 분배금(배당금)은 왜 분리과세 안 해주나요" 배당소득의 분리과세방안이 국회에서 논의중인 가운데 고배당 기업들..</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-11-03 08:53:08</t>
+          <t>2025-11-03 09:00:09</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583386</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041354</t>
         </is>
       </c>
     </row>
@@ -1511,27 +1511,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>“현금 쟁여놓은 버핏 속내가 궁금해”…버크셔, 올해 자사주 매입까지 중단</t>
+          <t>내 속만 타들어 가네…코스피 불 뿜는데 '코스닥 3000 시대' 언제 오나</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6개월새 주가 12% 떨어져도 매입 없어 버크셔 보유 현금 546조원 사상 최대치 투자자들 ‘미국 증시 고평가’ 신호로 해석 ‘투자의 ..</t>
+          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-11-03 08:52:08</t>
+          <t>2025-11-03 09:00:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583385</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272275</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한화시스템, 해외 기업도 찾는 K-방산 부품…목표가 11.7% 상향-iM</t>
+          <t>성장축 올라탄 종목은 따로 있다… 네 전문가가 밝힌 ‘현재 최우선 체크 종목’[진짜 주식 3부]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>급증하는 글로벌 방산 수요로 국내 방산 반체계/부품 업체를 찾는 해외 방산기업이 늘면서 한화시스템 수주가 증가할 것이라는 전망이 나왔다..</t>
+          <t>지난 10월 31일(금) 방송된 한국경제TV ‘진짜 주식 3부’에서는 신학수 전문가(MJ스탁), 한중연 전문가(에스엠티엠 컨설팅), 전..</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-11-03 08:39:09</t>
+          <t>2025-11-03 08:56:10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272256</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229280</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>관세부담 덜어낸 현대차...증권가 “주가 20% 이상 상승여력” [오늘 나온 보고서]</t>
+          <t>“순금에 이자가 붙는다고?”…‘하나골드신탁’ 연일 매진</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>美 자동차 관세 25%→15% 4분기 팰리세이드 출시하며 미국 시장서 ‘골든 사이클’시작 증권사들이 현대자동차 목표 주가를 31만원에서..</t>
+          <t>‘장롱금’ 140조 깨운다 ‘금 신탁’, 90분만에 40억 ‘완판’ 순금 100g 이상 맡기면 1.5% 이자 고액 자산가 증여 수단으로..</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-11-03 08:38:08</t>
+          <t>2025-11-03 08:53:08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583377</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583386</t>
         </is>
       </c>
     </row>
@@ -1601,27 +1601,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>젠슨 황과 '깐부 회동'에 삼성전자·네이버, 프리마켓서 강세</t>
+          <t>“현금 쟁여놓은 버핏 속내가 궁금해”…버크셔, 올해 자사주 매입까지 중단</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>삼성전자(005930)와 네이버(035420), 현대차(005380) 등 이른바 '깐부 회동' 수혜주가 넥스트레이드 프리마켓(오전 8시..</t>
+          <t>6개월새 주가 12% 떨어져도 매입 없어 버크셔 보유 현금 546조원 사상 최대치 투자자들 ‘미국 증시 고평가’ 신호로 해석 ‘투자의 ..</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-11-03 08:38:02</t>
+          <t>2025-11-03 08:52:08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580543</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583385</t>
         </is>
       </c>
     </row>
@@ -1631,27 +1631,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이재용·젠슨황 치맥 회동…증권가 '삼성·엔비디아 AI동맹 가시화'</t>
+          <t>한화시스템, 해외 기업도 찾는 K-방산 부품…목표가 11.7% 상향-iM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15년 만에 한국을 방문한 인공지능(AI) 반도체 기업 엔비디아의 최고경영자(CEO) 젠슨 황이 이재용 삼성전자 회장과 치맥 회동을 통..</t>
+          <t>급증하는 글로벌 방산 수요로 국내 방산 반체계/부품 업체를 찾는 해외 방산기업이 늘면서 한화시스템 수주가 증가할 것이라는 전망이 나왔다..</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-11-03 08:36:08</t>
+          <t>2025-11-03 08:39:09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041353</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272256</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>한국투자證 “풍산, 회복 가능한 어닝 쇼크… 목표가는 하향”</t>
+          <t>관세부담 덜어낸 현대차...증권가 “주가 20% 이상 상승여력” [오늘 나온 보고서]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국투자증권은 풍산에 대해 회복 가능한 어닝쇼크를 기록해 투자 포인트는 전혀 훼손되지 않았다고 3일 평했다. 그러면서 투자의견 ‘매수(..</t>
+          <t>美 자동차 관세 25%→15% 4분기 팰리세이드 출시하며 미국 시장서 ‘골든 사이클’시작 증권사들이 현대자동차 목표 주가를 31만원에서..</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-11-03 08:34:11</t>
+          <t>2025-11-03 08:38:08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119572</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583377</t>
         </is>
       </c>
     </row>
@@ -1691,27 +1691,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LS증권 "한화시스템 필리조선소 적자에도 목표가 8% 상향"[아침밥]</t>
+          <t>젠슨 황과 '깐부 회동'에 삼성전자·네이버, 프리마켓서 강세</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>머니S 증권전문기자들이 매일 아침 쏟아지는 증권사 리포트 중에서 가장 알찬 리포트의 핵심을 요약해 제공하는 '아침밥'을 통해 든든하게 ..</t>
+          <t>삼성전자(005930)와 네이버(035420), 현대차(005380) 등 이른바 '깐부 회동' 수혜주가 넥스트레이드 프리마켓(오전 8시..</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-03 08:33:07</t>
+          <t>2025-11-03 08:38:02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110730</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580543</t>
         </is>
       </c>
     </row>
@@ -1721,27 +1721,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>부동산 막히자 빨라진 ‘머니무브’…예금 빼서 증시로 [투자360]</t>
+          <t>이재용·젠슨황 치맥 회동…증권가 '삼성·엔비디아 AI동맹 가시화'</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>증시 사천피 불장에 자금 폭주 증시 대기자금 85조 ‘역대 최대’ 개인 매수세 확대 속 은행은 단기자금 이탈 지난달 12일 서울 시내의..</t>
+          <t>15년 만에 한국을 방문한 인공지능(AI) 반도체 기업 엔비디아의 최고경영자(CEO) 젠슨 황이 이재용 삼성전자 회장과 치맥 회동을 통..</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-11-03 08:30:11</t>
+          <t>2025-11-03 08:36:08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551397</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041353</t>
         </is>
       </c>
     </row>
@@ -1751,27 +1751,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>연준, 매파적 기조 확산 - [굿모닝 글로벌 이슈]</t>
+          <t>한국투자證 “풍산, 회복 가능한 어닝 쇼크… 목표가는 하향”</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>전일장 아마존의 호실적이 증시를 이끌며 반등했지만 연준 위원들의 매파적인 발언에 상승폭은 제한적이었습니다. 먼저, 지난 회의에서 ‘금리..</t>
+          <t>한국투자증권은 풍산에 대해 회복 가능한 어닝쇼크를 기록해 투자 포인트는 전혀 훼손되지 않았다고 3일 평했다. 그러면서 투자의견 ‘매수(..</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-11-03 08:30:08</t>
+          <t>2025-11-03 08:34:11</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229272</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119572</t>
         </is>
       </c>
     </row>
@@ -1781,27 +1781,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>국내외 불장에 정책 모멘텀까지…하나證 "증권株, 더 달린다"[마켓시그널]</t>
+          <t>LS증권 "한화시스템 필리조선소 적자에도 목표가 8% 상향"[아침밥]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>지난달 국내 증시의 일평균 거래대금이 2021년 1월 이후 최고치를 기록하고, 해외 주식 거래 규모마저 역대 최대치를 갈아치우면서 증권..</t>
+          <t>머니S 증권전문기자들이 매일 아침 쏟아지는 증권사 리포트 중에서 가장 알찬 리포트의 핵심을 요약해 제공하는 '아침밥'을 통해 든든하게 ..</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>머니S</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-11-03 08:29:09</t>
+          <t>2025-11-03 08:33:07</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551016</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001110730</t>
         </is>
       </c>
     </row>
@@ -1811,27 +1811,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>역사적 10월 후 '모멘텀 진공' 들어선 코스피…단기 변동성 확대 [오늘장 미리보기]</t>
+          <t>부동산 막히자 빨라진 ‘머니무브’…예금 빼서 증시로 [투자360]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>코스피지수가 4100포인트를 돌파하며 역사에 남을 10월을 마무리 한 가운데 11월 시장은 '모멘텀 진공상태'에 진입할 것이란 전망이 ..</t>
+          <t>증시 사천피 불장에 자금 폭주 증시 대기자금 85조 ‘역대 최대’ 개인 매수세 확대 속 은행은 단기자금 이탈 지난달 12일 서울 시내의..</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-11-03 08:25:11</t>
+          <t>2025-11-03 08:30:11</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205861</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551397</t>
         </is>
       </c>
     </row>
@@ -1841,27 +1841,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>iM證 “삼성물산, 원전·바이오·지배구조 개편 삼박자로 가치 성장 가속화”</t>
+          <t>연준, 매파적 기조 확산 - [굿모닝 글로벌 이슈]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>iM증권은 3일 삼성물산에 대해 원전, 바이오, 지배구조 개편 등으로 가치 성장이 가속화될 것이라고 전망했다. 목표 주가는 기존 18만..</t>
+          <t>전일장 아마존의 호실적이 증시를 이끌며 반등했지만 연준 위원들의 매파적인 발언에 상승폭은 제한적이었습니다. 먼저, 지난 회의에서 ‘금리..</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-11-03 08:23:08</t>
+          <t>2025-11-03 08:30:08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119570</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229272</t>
         </is>
       </c>
     </row>
@@ -1871,27 +1871,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"필리조선소, 핵잠 건조 조선소로 확장…한화시스템 목표가↑"-NH</t>
+          <t>국내외 불장에 정책 모멘텀까지…하나證 "증권株, 더 달린다"[마켓시그널]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 한화시스템의 목표주가를 6만8500원에서 7만3000원으로 높였다. 필리조선소가 향후 핵잠수함 건조로 업그레이드돼 ..</t>
+          <t>지난달 국내 증시의 일평균 거래대금이 2021년 1월 이후 최고치를 기록하고, 해외 주식 거래 규모마저 역대 최대치를 갈아치우면서 증권..</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-11-03 08:19:11</t>
+          <t>2025-11-03 08:29:09</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205859</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551016</t>
         </is>
       </c>
     </row>
@@ -1901,27 +1901,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"역대급으로 돈 잘 굴렸다"…'1300조 덩치가 최강 전략' 국민연금, 깜짝 등판한 곳[기금·공제 대해부]①</t>
+          <t>역사적 10월 후 '모멘텀 진공' 들어선 코스피…단기 변동성 확대 [오늘장 미리보기]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>편집자주연기금과 공제회가 자본시장의 핵심 플레이어로 자리매김한 지 오래다. 연기금과 공제회는 국민의 노후보장(연기금)과 회원들의 자산증..</t>
+          <t>코스피지수가 4100포인트를 돌파하며 역사에 남을 10월을 마무리 한 가운데 11월 시장은 '모멘텀 진공상태'에 진입할 것이란 전망이 ..</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-11-03 08:16:53</t>
+          <t>2025-11-03 08:25:11</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673330</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205861</t>
         </is>
       </c>
     </row>
@@ -1931,27 +1931,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>방산도 다 잘나가는 것 아니네…“풍산 목표가 19.3만→16만 ‘하향’”</t>
+          <t>iM證 “삼성물산, 원전·바이오·지배구조 개편 삼박자로 가치 성장 가속화”</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 풍산의 3분기 실적이 가이던스를 하회했으며 수익성 전망도 낮아 목표주가를 19만3000원에서 16만원으로 낮춰 잡았..</t>
+          <t>iM증권은 3일 삼성물산에 대해 원전, 바이오, 지배구조 개편 등으로 가치 성장이 가속화될 것이라고 전망했다. 목표 주가는 기존 18만..</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-11-03 08:13:53</t>
+          <t>2025-11-03 08:23:08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991024</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119570</t>
         </is>
       </c>
     </row>
@@ -1961,27 +1961,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>달러 강세와 증시 조정…환율 1430원대 안착[외환브리핑]</t>
+          <t>"필리조선소, 핵잠 건조 조선소로 확장…한화시스템 목표가↑"-NH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>원·달러 환율은 1430원대에서 안착을 시도할 것으로 전망된다. 글로벌 달러화 강세 압박이 재개하고, 고점 논란이 부상한 성장주 위험선..</t>
+          <t>NH투자증권은 3일 한화시스템의 목표주가를 6만8500원에서 7만3000원으로 높였다. 필리조선소가 향후 핵잠수함 건조로 업그레이드돼 ..</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-11-03 08:13:09</t>
+          <t>2025-11-03 08:19:11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154351</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205859</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>기아, 피지컬AI 본격화로 밸류 높아진다[클릭e종목]</t>
+          <t>"역대급으로 돈 잘 굴렸다"…'1300조 덩치가 최강 전략' 국민연금, 깜짝 등판한 곳[기금·공제 대해부]①</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3일 삼성증권은 기아에 대해 관세 불확실성 제거로 일본 경쟁사와 동등한 경쟁이 가능해졌고, 엔비디아와 협력으로 피지컬(Physical)..</t>
+          <t>편집자주연기금과 공제회가 자본시장의 핵심 플레이어로 자리매김한 지 오래다. 연기금과 공제회는 국민의 노후보장(연기금)과 회원들의 자산증..</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-11-03 08:08:07</t>
+          <t>2025-11-03 08:16:53</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673324</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673330</t>
         </is>
       </c>
     </row>
@@ -2021,27 +2021,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>트럼프 관세 운명, 美 대법으로…AMD·팔란티어 실적에 AI 낙관론도 시험대[글로벌마켓레이더]</t>
+          <t>방산도 다 잘나가는 것 아니네…“풍산 목표가 19.3만→16만 ‘하향’”</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>美 대법, 보복성 관세 위헌 여부 구두심리 셧다운 장기화 속 경기 부담 확대 전망 AMD·팔란티어 실적 발표 [로이터] [헤럴드경제=문..</t>
+          <t>NH투자증권은 3일 풍산의 3분기 실적이 가이던스를 하회했으며 수익성 전망도 낮아 목표주가를 19만3000원에서 16만원으로 낮춰 잡았..</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>디지털타임스</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-11-03 08:07:08</t>
+          <t>2025-11-03 08:13:53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551384</t>
+          <t>https://n.news.naver.com/mnews/article/029/0002991024</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"버핏의 버크셔가 이럴리 없는데"…美주식 고평가 신호?[뉴스새벽배송]</t>
+          <t>달러 강세와 증시 조정…환율 1430원대 안착[외환브리핑]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>‘투자의 귀재’ 워런 버핏 회장(사진)이 이끄는 버크셔 해서웨이(이하 버크셔)가 최근 주가 부진에도 불구하고 자사주를 전혀 매입하지 않..</t>
+          <t>원·달러 환율은 1430원대에서 안착을 시도할 것으로 전망된다. 글로벌 달러화 강세 압박이 재개하고, 고점 논란이 부상한 성장주 위험선..</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-11-03 08:05:13</t>
+          <t>2025-11-03 08:13:09</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154343</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154351</t>
         </is>
       </c>
     </row>
@@ -2081,27 +2081,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'슈퍼위크' 소화한 코스피 상승세 이어갈까…실적 관건[마켓뷰]</t>
+          <t>기아, 피지컬AI 본격화로 밸류 높아진다[클릭e종목]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>지난주 말 4,100선 첫 돌파…뉴욕증시도 3대 지수 강세 마감 '조·방·원' 실적 주시…단기 고점 부담에 '숨 고르기' 가능성도 아시..</t>
+          <t>3일 삼성증권은 기아에 대해 관세 불확실성 제거로 일본 경쟁사와 동등한 경쟁이 가능해졌고, 엔비디아와 협력으로 피지컬(Physical)..</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-11-03 08:04:12</t>
+          <t>2025-11-03 08:08:07</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0015719720</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673324</t>
         </is>
       </c>
     </row>
@@ -2111,27 +2111,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>신한 이수구, 누적 수익률 31%로 1위…효자 종목은 '두산'[스타워즈]</t>
+          <t>‘업토버’ 깨진 비트코인 11만달러 박스권…ETF 자금유출 [투자360]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>'2025 한경스타워즈 실전투자대회(하반기)' 6주차 신한투자증권의 이수구 대구금융센터 대리가 직전주에 이어 1위를 차지했다. 인공지능..</t>
+          <t>비트코인 이달 11만달러 전후 흐름 현물 ETF서 3거래일째 순매도세 [헤럴드경제=유동현 기자] ‘업토버(Uptober·10월 상승장)..</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-11-03 08:01:15</t>
+          <t>2025-11-03 08:07:11</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205855</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551385</t>
         </is>
       </c>
     </row>
@@ -2141,27 +2141,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>‘스팩 합병 상장’ 엔비알모션 “글로벌 베어링 선두 기업으로 도약”</t>
+          <t>트럼프 관세 운명, 美 대법으로…AMD·팔란티어 실적에 AI 낙관론도 시험대[글로벌마켓레이더]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>“엔비알모션은 수십 년간 일본·독일 등 해외 수입에 의존해 온 베어링 부품 시장에서 자체 기술로 국산화를 이끌어온 기업입니다. 지금은 ..</t>
+          <t>美 대법, 보복성 관세 위헌 여부 구두심리 셧다운 장기화 속 경기 부담 확대 전망 AMD·팔란티어 실적 발표 [로이터] [헤럴드경제=문..</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-11-03 08:01:09</t>
+          <t>2025-11-03 08:07:08</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154337</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551384</t>
         </is>
       </c>
     </row>
@@ -2171,27 +2171,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"이젠 우리 차례"…반도체·방산 중기, 'ABCD' 특례로 코스닥 간다</t>
+          <t>"버핏의 버크셔가 이럴리 없는데"…美주식 고평가 신호?[뉴스새벽배송]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
+          <t>‘투자의 귀재’ 워런 버핏 회장(사진)이 이끄는 버크셔 해서웨이(이하 버크셔)가 최근 주가 부진에도 불구하고 자사주를 전혀 매입하지 않..</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-03 08:00:00</t>
+          <t>2025-11-03 08:05:13</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272246</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154343</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2201,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>"LG화학, 내년 실적개선·LG엔솔 지분활용 기대"[클릭 e종목]</t>
+          <t>'슈퍼위크' 소화한 코스피 상승세 이어갈까…실적 관건[마켓뷰]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>iM증권은 3일 LG화학에 대해 "내년 석유화학 업황 회복과 첨단소재 성장으로 실적 개선이 예상된다"며 투자의견 매수를 유지하고, 목표..</t>
+          <t>지난주 말 4,100선 첫 돌파…뉴욕증시도 3대 지수 강세 마감 '조·방·원' 실적 주시…단기 고점 부담에 '숨 고르기' 가능성도 아시..</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-03 07:59:24</t>
+          <t>2025-11-03 08:04:12</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673317</t>
+          <t>https://n.news.naver.com/mnews/article/001/0015719720</t>
         </is>
       </c>
     </row>
@@ -2231,27 +2231,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>“필리조선소서 핵잠수함 건조”…한화시스템, 목표가 7%↑-NH</t>
+          <t>신한 이수구, 누적 수익률 31%로 1위…효자 종목은 '두산'[스타워즈]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 한화시스템(272210)에 대해 필리조선소가 향후 핵잠수함 건조 가능 조선소로 성장할 것이라며 목표주가를 7만 30..</t>
+          <t>'2025 한경스타워즈 실전투자대회(하반기)' 6주차 신한투자증권의 이수구 대구금융센터 대리가 직전주에 이어 1위를 차지했다. 인공지능..</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-11-03 07:56:17</t>
+          <t>2025-11-03 08:01:15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154333</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205855</t>
         </is>
       </c>
     </row>
@@ -2261,27 +2261,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>"이젠 우리 차례"…반도체·방산 중기, 'ABCD' 특례로 코스닥 간다</t>
+          <t>‘스팩 합병 상장’ 엔비알모션 “글로벌 베어링 선두 기업으로 도약”</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
+          <t>“엔비알모션은 수십 년간 일본·독일 등 해외 수입에 의존해 온 베어링 부품 시장에서 자체 기술로 국산화를 이끌어온 기업입니다. 지금은 ..</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-03 08:00:00</t>
+          <t>2025-11-03 08:01:09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272246</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154337</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>"LG화학, 내년 실적개선·LG엔솔 지분활용 기대"[클릭 e종목]</t>
+          <t>"이젠 우리 차례"…반도체·방산 중기, 'ABCD' 특례로 코스닥 간다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>iM증권은 3일 LG화학에 대해 "내년 석유화학 업황 회복과 첨단소재 성장으로 실적 개선이 예상된다"며 투자의견 매수를 유지하고, 목표..</t>
+          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-11-03 07:59:24</t>
+          <t>2025-11-03 08:00:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673317</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272246</t>
         </is>
       </c>
     </row>
@@ -2321,27 +2321,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>“필리조선소서 핵잠수함 건조”…한화시스템, 목표가 7%↑-NH</t>
+          <t>"LG화학, 내년 실적개선·LG엔솔 지분활용 기대"[클릭 e종목]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 한화시스템(272210)에 대해 필리조선소가 향후 핵잠수함 건조 가능 조선소로 성장할 것이라며 목표주가를 7만 30..</t>
+          <t>iM증권은 3일 LG화학에 대해 "내년 석유화학 업황 회복과 첨단소재 성장으로 실적 개선이 예상된다"며 투자의견 매수를 유지하고, 목표..</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-03 07:56:17</t>
+          <t>2025-11-03 07:59:24</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154333</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673317</t>
         </is>
       </c>
     </row>
@@ -2351,27 +2351,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"SK이노베이션, 美 ESS 진출 고무적이나 아쉬운 규모"[클릭 e종목]</t>
+          <t>“필리조선소서 핵잠수함 건조”…한화시스템, 목표가 7%↑-NH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>iM증권은 3일 SK이노베이션의 목표주가를 14만8000원으로 상향했다. 다만, 국내 경쟁사들 대비 중장기 에너지저장장치(ESS) 설비..</t>
+          <t>NH투자증권은 3일 한화시스템(272210)에 대해 필리조선소가 향후 핵잠수함 건조 가능 조선소로 성장할 것이라며 목표주가를 7만 30..</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-03 07:55:53</t>
+          <t>2025-11-03 07:56:17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673315</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154333</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LG전자, 1분기부터 반등 기대…목표가 16%↑-iM</t>
+          <t>"SK이노베이션, 美 ESS 진출 고무적이나 아쉬운 규모"[클릭 e종목]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>iM증권은 LG전자(066570)에 대해 4분기 부진한 실적을 기록한 뒤 2026년 1분기부터는 성수기와 경영 효율화 효과가 반영될 것..</t>
+          <t>iM증권은 3일 SK이노베이션의 목표주가를 14만8000원으로 상향했다. 다만, 국내 경쟁사들 대비 중장기 에너지저장장치(ESS) 설비..</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-03 07:52:15</t>
+          <t>2025-11-03 07:55:53</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154329</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673315</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LG화학, 실적 개선ㆍLGES 지분 활용 기대...목표주가 50만원↑-iM</t>
+          <t>LG전자, 1분기부터 반등 기대…목표가 16%↑-iM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>iM증권은 3일 LG화학(051910)에 대해 목표주가를 37만원에서 50만원으로 상향하고 투자의견 매수를 유지했다. 전유진 iM증권 ..</t>
+          <t>iM증권은 LG전자(066570)에 대해 4분기 부진한 실적을 기록한 뒤 2026년 1분기부터는 성수기와 경영 효율화 효과가 반영될 것..</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-03 07:49:08</t>
+          <t>2025-11-03 07:52:15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154327</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154329</t>
         </is>
       </c>
     </row>
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>"삼성전자, 엔비디아와 AI 동맹…메모리 사업 시너지 기대"-</t>
+          <t>LG화학, 실적 개선ㆍLGES 지분 활용 기대...목표주가 50만원↑-iM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KB증권은 3일 삼성전자에 대해 "엔비디아와의 세계 최대 인공지능(AI) 팩토리 구축 협력으로 메모리 사업의 시너지 효과가 기대된다"고..</t>
+          <t>iM증권은 3일 LG화학(051910)에 대해 목표주가를 37만원에서 50만원으로 상향하고 투자의견 매수를 유지했다. 전유진 iM증권 ..</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-03 07:46:16</t>
+          <t>2025-11-03 07:49:08</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205849</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154327</t>
         </is>
       </c>
     </row>
@@ -2471,27 +2471,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5000피 향해 달리는 국장…외인들 '이 업종' 꽂혔다</t>
+          <t>"삼성전자, 엔비디아와 AI 동맹…메모리 사업 시너지 기대"-</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>코스피 과열 부담에도 중장기적으로 우상향 기조를 유지하고, 이 가운데 주도 업종인 IT가 지수 상승을 견인할 것이라는 전망이 나왔다. ..</t>
+          <t>KB증권은 3일 삼성전자에 대해 "엔비디아와의 세계 최대 인공지능(AI) 팩토리 구축 협력으로 메모리 사업의 시너지 효과가 기대된다"고..</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-03 07:45:08</t>
+          <t>2025-11-03 07:46:16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154325</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205849</t>
         </is>
       </c>
     </row>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>"GPU 26만장 확보로 AI 언어모델 및 서비스 개발 탄력"-하나</t>
+          <t>5000피 향해 달리는 국장…외인들 '이 업종' 꽂혔다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>하나증권은 3일 한국 정부와 기업이 엔비디아 그래픽카드(GPU) 26만장을 확보한 것과 관련해 "주요 산업에서 인공지능(AI) 개발과 ..</t>
+          <t>코스피 과열 부담에도 중장기적으로 우상향 기조를 유지하고, 이 가운데 주도 업종인 IT가 지수 상승을 견인할 것이라는 전망이 나왔다. ..</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-11-03 07:43:10</t>
+          <t>2025-11-03 07:45:08</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205848</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154325</t>
         </is>
       </c>
     </row>
@@ -2531,27 +2531,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성전자·엔비디아 협력에…KB證, “삼성에스디에스, 신규 사업 기회”</t>
+          <t>"GPU 26만장 확보로 AI 언어모델 및 서비스 개발 탄력"-하나</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KB증권은 3일 삼성에스디에스(삼성SDS)에 대해 삼성전자와 엔비디아가 구축하기로 한 인공지능(AI) 팩토리에 직접 관여된 실무 사업자..</t>
+          <t>하나증권은 3일 한국 정부와 기업이 엔비디아 그래픽카드(GPU) 26만장을 확보한 것과 관련해 "주요 산업에서 인공지능(AI) 개발과 ..</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-11-03 07:42:09</t>
+          <t>2025-11-03 07:43:10</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119566</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205848</t>
         </is>
       </c>
     </row>
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>"한 주에 280만원 간다"…'황제주 중의 황제' 파격 전망</t>
+          <t>삼성전자·엔비디아 협력에…KB證, “삼성에스디에스, 신규 사업 기회”</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>한국투자증권은 3일 효성중공업(298040)에 대해 글로벌 전력기기 업체 중 가장 빠르게, 가장 많이 성장하는 기업이라며 목표주가를 2..</t>
+          <t>KB증권은 3일 삼성에스디에스(삼성SDS)에 대해 삼성전자와 엔비디아가 구축하기로 한 인공지능(AI) 팩토리에 직접 관여된 실무 사업자..</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-03 07:39:08</t>
+          <t>2025-11-03 07:42:09</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154322</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119566</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>기아, 4분기부터 반등 시작…목표가 11%↑-NH</t>
+          <t>"한 주에 280만원 간다"…'황제주 중의 황제' 파격 전망</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NH투자증권은 기아(000270)에 대해 4분기부터 본격적인 신차 출시 사이클에 돌입해 반등이 기대된다고 분석했다. 투자의견 ‘매수(B..</t>
+          <t>한국투자증권은 3일 효성중공업(298040)에 대해 글로벌 전력기기 업체 중 가장 빠르게, 가장 많이 성장하는 기업이라며 목표주가를 2..</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-03 07:37:08</t>
+          <t>2025-11-03 07:39:08</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154321</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154322</t>
         </is>
       </c>
     </row>
@@ -2621,27 +2621,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한투證 “효성중공업, 美 매출 계속 성장할 것 …목표가 55%↑”</t>
+          <t>기아, 4분기부터 반등 시작…목표가 11%↑-NH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한국투자증권은 3일 효성중공업에 대해 미국 매출 비중이 계속 성장할 것이라며 목표 주가를 높여 잡았다. 투자 의견 ‘매수(Buy)’를 ..</t>
+          <t>NH투자증권은 기아(000270)에 대해 4분기부터 본격적인 신차 출시 사이클에 돌입해 반등이 기대된다고 분석했다. 투자의견 ‘매수(B..</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-03 07:25:07</t>
+          <t>2025-11-03 07:37:08</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119564</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154321</t>
         </is>
       </c>
     </row>
@@ -2651,27 +2651,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>심팩 최진식 중견련 회장, 홍영표 전 의원 무슨 관계?[거버넌스워치]</t>
+          <t>한투證 “효성중공업, 美 매출 계속 성장할 것 …목표가 55%↑”</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>산업용 프레스 및 합금철을 주력으로 하는 중견그룹 심팩(SIMPAC)의 2대(代) 세습 작업이 재개됐다. 중견기업연합회 회장인 사주(社..</t>
+          <t>한국투자증권은 3일 효성중공업에 대해 미국 매출 비중이 계속 성장할 것이라며 목표 주가를 높여 잡았다. 투자 의견 ‘매수(Buy)’를 ..</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-11-03 07:10:07</t>
+          <t>2025-11-03 07:25:07</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041349</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119564</t>
         </is>
       </c>
     </row>
@@ -2681,27 +2681,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>"삼성전자, 더 오를 수 있다"…전문가 조언 들어보니 [인터뷰+]</t>
+          <t>심팩 최진식 중견련 회장, 홍영표 전 의원 무슨 관계?[거버넌스워치]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>'한국에 투자할 종목이 많다'는 게 최근 글로벌 투자업계 관계자들의 반응입니다." 정성한 신한자산운용 주식투자운용본부장은 2일 한국경제..</t>
+          <t>산업용 프레스 및 합금철을 주력으로 하는 중견그룹 심팩(SIMPAC)의 2대(代) 세습 작업이 재개됐다. 중견기업연합회 회장인 사주(社..</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-11-03 07:01:12</t>
+          <t>2025-11-03 07:10:07</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205840</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041349</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>위츠, GS와 손잡는다…“3년 내 전기차 충전기 매출 1000억”</t>
+          <t>"삼성전자, 더 오를 수 있다"…전문가 조언 들어보니 [인터뷰+]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>위츠, GS서 50억 투자 유치 미래 모빌리티 동맹 맺어 “GS차지비와 전기차 충전 협력 전기차 충전기 매출 1000억 목표” EV무선..</t>
+          <t>'한국에 투자할 종목이 많다'는 게 최근 글로벌 투자업계 관계자들의 반응입니다." 정성한 신한자산운용 주식투자운용본부장은 2일 한국경제..</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-11-03 07:01:10</t>
+          <t>2025-11-03 07:01:12</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205839</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205840</t>
         </is>
       </c>
     </row>
@@ -2741,27 +2741,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'드디어 관세 족쇄 풀었다'…'30만원 눈앞' 액셀 밟는 현대차 주가</t>
+          <t>위츠, GS와 손잡는다…“3년 내 전기차 충전기 매출 1000억”</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>현대차가 관세 우려 완화에 따라 주가 상승세가 이어지며 30만원 돌파를 눈앞에 뒀다. 3일 한국거래소에 따르면 현대차는 지난달 31일 ..</t>
+          <t>위츠, GS서 50억 투자 유치 미래 모빌리티 동맹 맺어 “GS차지비와 전기차 충전 협력 전기차 충전기 매출 1000억 목표” EV무선..</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-11-03 06:55:00</t>
+          <t>2025-11-03 07:01:10</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673293</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205839</t>
         </is>
       </c>
     </row>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>국민연금, ‘오천피’에 ‘사상 최고’ 美 증시 타고 고갈 걱정 털어내나…주식 비중 50% 시대 개막 [투자360]</t>
+          <t>'드디어 관세 족쇄 풀었다'…'30만원 눈앞' 액셀 밟는 현대차 주가</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>‘안정’의 채권 줄이고 ‘수익’의 주식으로 1269조 ‘연금 고래’, 세계 시장으로 국내 증시 ‘과잉 영향력’ 해소 노후 자금 전략 대..</t>
+          <t>현대차가 관세 우려 완화에 따라 주가 상승세가 이어지며 30만원 돌파를 눈앞에 뒀다. 3일 한국거래소에 따르면 현대차는 지난달 31일 ..</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-11-03 06:48:09</t>
+          <t>2025-11-03 06:55:00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551356</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673293</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>버핏이 볼 때 지금 주식 시장은 너무 고평가?…올해 자사주 매입 ‘제로’·현금 보유 ‘사상 최고 [투자360]</t>
+          <t>국민연금, ‘오천피’에 ‘사상 최고’ 美 증시 타고 고갈 걱정 털어내나…주식 비중 50% 시대 개막 [투자360]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6개월새 주가 12% 떨어졌는데 매입 없어 현금은 546조원 ‘사상최고’ 워런 버핏 버크셔해서웨이 회장. [AP·게티이미지뱅크] [헤럴..</t>
+          <t>‘안정’의 채권 줄이고 ‘수익’의 주식으로 1269조 ‘연금 고래’, 세계 시장으로 국내 증시 ‘과잉 영향력’ 해소 노후 자금 전략 대..</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-11-03 06:42:09</t>
+          <t>2025-11-03 06:48:09</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551352</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551356</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>"삼성전자, 지금이라도 사? 말아?"…'포모 vs 트라우마' 갈팡질팡 개미들</t>
+          <t>버핏이 볼 때 지금 주식 시장은 너무 고평가?…올해 자사주 매입 ‘제로’·현금 보유 ‘사상 최고 [투자360]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>삼성전자가 연일 사상 최고가를 경신하면서 개미투자자들은 "지금이라도 사야 한다"는 '포모(FOMO·나만 돈 못 번다는 공포)'와 "물리..</t>
+          <t>6개월새 주가 12% 떨어졌는데 매입 없어 현금은 546조원 ‘사상최고’ 워런 버핏 버크셔해서웨이 회장. [AP·게티이미지뱅크] [헤럴..</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-11-03 06:40:00</t>
+          <t>2025-11-03 06:42:09</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580413</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551352</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>“주식하고 비교하면 아직 저렴” 쉬었던 금값 다시 꿈틀 [줍줍 리포트]</t>
+          <t>"삼성전자, 지금이라도 사? 말아?"…'포모 vs 트라우마' 갈팡질팡 개미들</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한동안 사상 최고가를 연일 경신하다가 하락 전환 후 잠시 주춤했던 금값이 다시 오를 조짐을 보이고 있다. 전문가들은 일시적인 기술적 조..</t>
+          <t>삼성전자가 연일 사상 최고가를 경신하면서 개미투자자들은 "지금이라도 사야 한다"는 '포모(FOMO·나만 돈 못 번다는 공포)'와 "물리..</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-11-03 06:31:07</t>
+          <t>2025-11-03 06:40:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550980</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580413</t>
         </is>
       </c>
     </row>
@@ -2891,27 +2891,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>"사천피 넘어 4100까지 갈줄이야"…혼돈의 개미들, 다시 증시 '기웃'</t>
+          <t>“주식하고 비교하면 아직 저렴” 쉬었던 금값 다시 꿈틀 [줍줍 리포트]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>코스피가 '사천피' 달성 1주일도 안 돼 4100선까지 치솟았다. 중장기 상승세가 이어질 것이란 전망에 그간 증시를 관망하던 개인투자자..</t>
+          <t>한동안 사상 최고가를 연일 경신하다가 하락 전환 후 잠시 주춤했던 금값이 다시 오를 조짐을 보이고 있다. 전문가들은 일시적인 기술적 조..</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-11-03 06:20:00</t>
+          <t>2025-11-03 06:31:07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580403</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550980</t>
         </is>
       </c>
     </row>
@@ -2921,27 +2921,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>'투자의 달인' 버핏 투자사, 중대 결정…'헉'</t>
+          <t>"사천피 넘어 4100까지 갈줄이야"…혼돈의 개미들, 다시 증시 '기웃'</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>'오마하의 현인'으로 불리는 워런 버핏(95) 회장의 버크셔 해서웨이(이하 버크셔)가 최근 자사주를 전혀 매입하지 않은 것으로 확인됐다..</t>
+          <t>코스피가 '사천피' 달성 1주일도 안 돼 4100선까지 치솟았다. 중장기 상승세가 이어질 것이란 전망에 그간 증시를 관망하던 개인투자자..</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-11-03 06:16:55</t>
+          <t>2025-11-03 06:20:00</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229262</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580403</t>
         </is>
       </c>
     </row>
@@ -2951,27 +2951,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>공시 위반 반복되는데… 깜깜이 주식 거래 막는 감시 시스템 없어</t>
+          <t>'투자의 달인' 버핏 투자사, 중대 결정…'헉'</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>주식 거래 자동 통보시스템 갖추고도 5%룰 위반 반복 본인과 특수관계인을 더해 발행 주식의 5% 이상을 보유한 주주에게 부여된 지분 공..</t>
+          <t>'오마하의 현인'으로 불리는 워런 버핏(95) 회장의 버크셔 해서웨이(이하 버크셔)가 최근 자사주를 전혀 매입하지 않은 것으로 확인됐다..</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-11-03 06:02:17</t>
+          <t>2025-11-03 06:16:55</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119555</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229262</t>
         </is>
       </c>
     </row>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>‘AI 경량화’ 노타 상장…‘아기상어’ 더핑크퐁컴퍼니 공모 [이런주 증시 캘린더]</t>
+          <t>공시 위반 반복되는데… 깜깜이 주식 거래 막는 감시 시스템 없어</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>이번 주 국내 증시에서는 인공지능(AI) 기술 업체인 노타가 코스닥 시장에 상장한다. ‘아기상어’ 등으로 유명한 더핑크퐁컴퍼니는 상장을..</t>
+          <t>주식 거래 자동 통보시스템 갖추고도 5%룰 위반 반복 본인과 특수관계인을 더해 발행 주식의 5% 이상을 보유한 주주에게 부여된 지분 공..</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:18</t>
+          <t>2025-11-03 06:02:17</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550977</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119555</t>
         </is>
       </c>
     </row>
@@ -3011,27 +3011,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>"해외 금융기관들, 코스피 추가 상승 우세하다고 전망"</t>
+          <t>‘AI 경량화’ 노타 상장…‘아기상어’ 더핑크퐁컴퍼니 공모 [이런주 증시 캘린더]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>코스피가 지난달 4000선을 돌파하면서 증권가에선 5000선을 넘보는 전망과 가격 부담에 대한 우려가 혼재한 상황이다. 그러나 대부분의..</t>
+          <t>이번 주 국내 증시에서는 인공지능(AI) 기술 업체인 노타가 코스닥 시장에 상장한다. ‘아기상어’ 등으로 유명한 더핑크퐁컴퍼니는 상장을..</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>파이낸셜뉴스</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:14</t>
+          <t>2025-11-03 06:01:18</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005428360</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550977</t>
         </is>
       </c>
     </row>
@@ -3041,27 +3041,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>쉬지 않고 내달린 코스피, 숨 고르기 할까…상승 모멘텀은 계속 [주간 증시 전망]</t>
+          <t>"해외 금융기관들, 코스피 추가 상승 우세하다고 전망"</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>코스피 지수가 사상 최초로 4100선에 도달한 가운데 과열 부담을 해소하기 위해 한 차례 숨 고르기를 할 것이라는 전망이 나온다. 다만..</t>
+          <t>코스피가 지난달 4000선을 돌파하면서 증권가에선 5000선을 넘보는 전망과 가격 부담에 대한 우려가 혼재한 상황이다. 그러나 대부분의..</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:07</t>
+          <t>2025-11-03 06:01:14</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550973</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005428360</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3071,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>‘사모펀드 대주주’ 법안 봇물...먹튀 사라질까</t>
+          <t>쉬지 않고 내달린 코스피, 숨 고르기 할까…상승 모멘텀은 계속 [주간 증시 전망]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>국내에서 사모펀드(PE)에 대한 인식은 대체로 좋지 않은 편이다. 지난 1997년 외환위기 직후 론스타 등 외국계 사모펀드들은 대기업 ..</t>
+          <t>코스피 지수가 사상 최초로 4100선에 도달한 가운데 과열 부담을 해소하기 위해 한 차례 숨 고르기를 할 것이라는 전망이 나온다. 다만..</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-11-03 06:00:09</t>
+          <t>2025-11-03 06:01:07</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087371</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550973</t>
         </is>
       </c>
     </row>
@@ -3101,27 +3101,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4100선 안착한 코스피, 숨고르기 구간 진입 “수익 방어할 때”</t>
+          <t>‘사모펀드 대주주’ 법안 봇물...먹튀 사라질까</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>코스피가 4100선을 지키며 상승 흐름을 이어갔다. 미국의 금리 인하와 미·중 정상회담 기대감, 반도체 업종의 호실적이 증시를 지탱한 ..</t>
+          <t>국내에서 사모펀드(PE)에 대한 인식은 대체로 좋지 않은 편이다. 지난 1997년 외환위기 직후 론스타 등 외국계 사모펀드들은 대기업 ..</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-11-03 05:35:00</t>
+          <t>2025-11-03 06:00:09</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991013</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087371</t>
         </is>
       </c>
     </row>
@@ -3131,27 +3131,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>이제 첫 월급 받았는데 노후대비가 웬 말?… "TDF는 달라"</t>
+          <t>4100선 안착한 코스피, 숨고르기 구간 진입 “수익 방어할 때”</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>#1. 2025년 첫 직장을 구한 A씨(28)는 카드 명세서를 보고 고민에 빠졌다. 사회 진출이 남보다 늦은 만큼 모은 돈은 적은데 씀..</t>
+          <t>코스피가 4100선을 지키며 상승 흐름을 이어갔다. 미국의 금리 인하와 미·중 정상회담 기대감, 반도체 업종의 호실적이 증시를 지탱한 ..</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>디지털타임스</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-11-03 05:00:00</t>
+          <t>2025-11-03 05:35:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110710</t>
+          <t>https://n.news.naver.com/mnews/article/029/0002991013</t>
         </is>
       </c>
     </row>
@@ -3161,27 +3161,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AI열풍에 '전자산업 쌀' 풍년… 삼성전기 '뜨끈'</t>
+          <t>이제 첫 월급 받았는데 노후대비가 웬 말?… "TDF는 달라"</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AI(인공지능) 열풍이 반도체 대형주를 넘어 부품, 기판주로 확산한다. 삼성전기가 수혜주로 부상하고 있다. 테슬라 AI칩 공급계약 이후..</t>
+          <t>#1. 2025년 첫 직장을 구한 A씨(28)는 카드 명세서를 보고 고민에 빠졌다. 사회 진출이 남보다 늦은 만큼 모은 돈은 적은데 씀..</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>머니S</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-11-03 04:03:00</t>
+          <t>2025-11-03 05:00:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272178</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001110710</t>
         </is>
       </c>
     </row>
@@ -3191,25 +3191,55 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>AI열풍에 '전자산업 쌀' 풍년… 삼성전기 '뜨끈'</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AI(인공지능) 열풍이 반도체 대형주를 넘어 부품, 기판주로 확산한다. 삼성전기가 수혜주로 부상하고 있다. 테슬라 AI칩 공급계약 이후..</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>머니투데이</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2025-11-03 04:03:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005272178</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>투심 몰린 파인트리, '렉라자 잡을까' 기대 후보[바이오 다크호스 펀딩]</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>한 주(10월 27일~10월 31일) 제약·바이오 업계에서 주목받은 투자 소식이다. 국내에서는 4곳 이상의 신약개발사가 진행하던 투자라..</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>이데일리</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>2025-11-03 01:00:13</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/018/0006154273</t>
         </is>

--- a/data/증권뉴스_2025-11-03.xlsx
+++ b/data/증권뉴스_2025-11-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>큰손 개미의 귀환 '코스피 불장' 원인?…달라붙은 종목은</t>
+          <t>[속보] 코스피, 4200선도 넘었다</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>코스피가 사상 처음 4,000선을 돌파한 이후 랠리를 이어가자, 거액을 운용하는 개인투자자들의 주식시장 참여가 크게 늘어난 것으로 나타..</t>
+          <t>파죽지세로 상승 중인 코스피 지수가 3일 2%대 오르며 4200선도 넘겼다. 이날 오전 11시 58분 기준 코스피 지수는 전 거래일 대..</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-11-03 11:30:15</t>
+          <t>2025-11-03 12:00:09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087399</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119664</t>
         </is>
       </c>
     </row>
@@ -491,27 +491,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>‘불장’코스피…반도체·2차전지 섹터만 랠리</t>
+          <t>초고수, '목표가 100만 원' SK하닉 폭풍 매수…삼전은 순매도 1위[주식 초고수는 지금]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KRX 35개 지수 중 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 지난 한 달간 코스피가..</t>
+          <t>미래에셋증권에서 거래하는 고수익 투자자들이 3일 오전 가장 많이 순매수한 종목은 SK하이닉스(000660), 한화솔루션(009830),..</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-11-03 11:22:15</t>
+          <t>2025-11-03 11:41:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551685</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551169</t>
         </is>
       </c>
     </row>
@@ -521,27 +521,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>초고수, 잇단 목표주가 상승에 SK하이닉스 매수 [주식 초고수는 지금]</t>
+          <t>큰손 개미의 귀환 '코스피 불장' 원인?…달라붙은 종목은</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>日노무라, SK하닉 목표주가 84만원 제시 SK증권서는 목표주가 100만원으로 상향 네이버, 레인보우로보틱스도 순매수 호재 이어졌던 현..</t>
+          <t>코스피가 사상 처음 4,000선을 돌파한 이후 랠리를 이어가자, 거액을 운용하는 개인투자자들의 주식시장 참여가 크게 늘어난 것으로 나타..</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-11-03 11:21:14</t>
+          <t>2025-11-03 11:30:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583517</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087399</t>
         </is>
       </c>
     </row>
@@ -551,27 +551,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코스피, 2% 넘게 올라 사상 최고치…4200선 눈앞</t>
+          <t>‘불장’코스피…반도체·2차전지 섹터만 랠리</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>코스피지수가 3일 장중 2% 넘게 상승폭을 확대해 사상 처음으로 4190선을 넘어섰다. 아시아태평양경제협력체(APEC) 회의를 계기로 ..</t>
+          <t>KRX 35개 지수 중 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 지난 한 달간 코스피가..</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-11-03 11:18:19</t>
+          <t>2025-11-03 11:22:15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005206018</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551685</t>
         </is>
       </c>
     </row>
@@ -581,27 +581,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"20% 더 오른다"…개미들 반년간 2.7조 '폭풍매수' 나선 종목</t>
+          <t>초고수, 잇단 목표주가 상승에 SK하이닉스 매수 [주식 초고수는 지금]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>네이버와 카카오가 하반기 들어 오름폭을 확대하고 있다. 인공지능(AI) 사업 성장과 실적 개선 기대가 커지면서 매수세가 유입되고 있다...</t>
+          <t>日노무라, SK하닉 목표주가 84만원 제시 SK증권서는 목표주가 100만원으로 상향 네이버, 레인보우로보틱스도 순매수 호재 이어졌던 현..</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-11-03 11:14:14</t>
+          <t>2025-11-03 11:21:14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005206017</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583517</t>
         </is>
       </c>
     </row>
@@ -611,27 +611,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>“지금도 안 늦었을까요?”…‘50만닉스’ 열흘 만 ‘60만닉스’ 돌파에 ‘100만닉스’ 목표가까지 [종목Pick]</t>
+          <t>코스피, 2% 넘게 올라 사상 최고치…4200선 눈앞</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>“이미 엄청난 속도로 올랐지만 SK하이닉스 주가는 더 오를 것이란 사람들이 많던데요. 지금 투자하는 건 늦지 않은 걸까요?”(직장인 A..</t>
+          <t>코스피지수가 3일 장중 2% 넘게 상승폭을 확대해 사상 처음으로 4190선을 넘어섰다. 아시아태평양경제협력체(APEC) 회의를 계기로 ..</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-11-03 11:10:19</t>
+          <t>2025-11-03 11:18:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551645</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005206018</t>
         </is>
       </c>
     </row>
@@ -641,27 +641,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>‘서로 밥도 안 먹던’ 상업·한일은행 동우회 26년 만에 통합</t>
+          <t>"20% 더 오른다"…개미들 반년간 2.7조 '폭풍매수' 나선 종목</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>‘우리은행 동우회’로 통합 출범, 고질적 계파 문화 사라질까 주목 1999년 한일은행과 상업은행이 통합해 출범한 우리은행이 26년 만에..</t>
+          <t>네이버와 카카오가 하반기 들어 오름폭을 확대하고 있다. 인공지능(AI) 사업 성장과 실적 개선 기대가 커지면서 매수세가 유입되고 있다...</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-11-03 11:08:26</t>
+          <t>2025-11-03 11:14:14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003938571</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005206017</t>
         </is>
       </c>
     </row>
@@ -671,27 +671,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>꼼수 막아야지... 자사주 소각 의무화 대상에 신탁 통한 간접 취득도 포함</t>
+          <t>“지금도 안 늦었을까요?”…‘50만닉스’ 열흘 만 ‘60만닉스’ 돌파에 ‘100만닉스’ 목표가까지 [종목Pick]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정부와 여당이 ‘자사주 의무 소각’을 골자로 한 3차 상법 개정안을 추진 중인 가운데, 신탁 계약을 통해 간접 취득한 자사주도 소각 대..</t>
+          <t>“이미 엄청난 속도로 올랐지만 SK하이닉스 주가는 더 오를 것이란 사람들이 많던데요. 지금 투자하는 건 늦지 않은 걸까요?”(직장인 A..</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-11-03 11:01:19</t>
+          <t>2025-11-03 11:10:19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119648</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551645</t>
         </is>
       </c>
     </row>
@@ -701,27 +701,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"효성중공업, 목표주가 300만원" 100% 상향... 현대차, 美하이브리드시장 진격 [株토피아]</t>
+          <t>‘서로 밥도 안 먹던’ 상업·한일은행 동우회 26년 만에 통합</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11월 3일 오전, 주요 증권사 리포트를 정리해드립니다. 삼성물산은 원전·바이오 등 신성장동력에 더해 지배구조 개선 기대감이 반영되며 ..</t>
+          <t>‘우리은행 동우회’로 통합 출범, 고질적 계파 문화 사라질까 주목 1999년 한일은행과 상업은행이 통합해 출범한 우리은행이 26년 만에..</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>파이낸셜뉴스</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11-03 11:01:16</t>
+          <t>2025-11-03 11:08:26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005428584</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003938571</t>
         </is>
       </c>
     </row>
@@ -731,27 +731,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엔비디아 GPU 5만장씩 'AI동맹'…'60만닉스' 탄생 '11만전자' 눈앞</t>
+          <t>'PBR 아닌 PER'…반도체株 평가 기준 바뀌었다 [심성미의 증시 돋보기]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>코스피가 장중 사상 최고치를 잇달아 경신하고 있다. SK하이닉스는 엔비디아발 AI(인공지능) 훈풍으로 주당 60만원에 거래되기도 했다...</t>
+          <t>메모리 반도체 기업의 가치 평가 기준으로 주가순자산비율(PBR)이 아닌 주가수익비율(PER)을 적용한 첫 사례가 나왔다. 3일 SK증권..</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-11-03 10:56:36</t>
+          <t>2025-11-03 11:06:18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272407</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005206011</t>
         </is>
       </c>
     </row>
@@ -761,27 +761,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'10만전자·60만닉스' 랠리…홍콩 레버리지 ETF로 돈 몰린다</t>
+          <t>꼼수 막아야지... 자사주 소각 의무화 대상에 신탁 통한 간접 취득도 포함</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>삼성전자와 SK하이닉스가 나란히 사상 최고가를 경신하며 고공행진을 이어가는 가운데, 이들 종목을 기초자산으로 한 해외 레버리지 상장지수..</t>
+          <t>정부와 여당이 ‘자사주 의무 소각’을 골자로 한 3차 상법 개정안을 추진 중인 가운데, 신탁 계약을 통해 간접 취득한 자사주도 소각 대..</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>뉴시스</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-11-03 10:54:44</t>
+          <t>2025-11-03 11:01:19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0013576788</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119648</t>
         </is>
       </c>
     </row>
@@ -791,27 +791,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>사상 최초 ‘60만닉스’ 터치…‘엔비디아 동맹’ 韓 AI 대표주 ‘불기둥’ [투자360]</t>
+          <t>"효성중공업, 목표주가 300만원" 100% 상향... 현대차, 美하이브리드시장 진격 [株토피아]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>이재명 대통령이 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자 접견에 앞서 국내 기업 대표들과 함께 기..</t>
+          <t>11월 3일 오전, 주요 증권사 리포트를 정리해드립니다. 삼성물산은 원전·바이오 등 신성장동력에 더해 지배구조 개선 기대감이 반영되며 ..</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-11-03 10:46:19</t>
+          <t>2025-11-03 11:01:16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551595</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005428584</t>
         </is>
       </c>
     </row>
@@ -821,27 +821,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"젠슨 황 엔비디아 CEO, 10억달러 자사주 현금화"</t>
+          <t>엔비디아 GPU 5만장씩 'AI동맹'…'60만닉스' 탄생 '11만전자' 눈앞</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인공지능(AI) 붐과 함께 승승장구 중인 엔비디아의 젠슨 황 최고경영자(CEO)가 지난 6월 이후 10억달러가 넘는 자사주를 현금화했다..</t>
+          <t>코스피가 장중 사상 최고치를 잇달아 경신하고 있다. SK하이닉스는 엔비디아발 AI(인공지능) 훈풍으로 주당 60만원에 거래되기도 했다...</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-11-03 10:42:25</t>
+          <t>2025-11-03 10:56:36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673522</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272407</t>
         </is>
       </c>
     </row>
@@ -851,27 +851,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>사상 초유의 60만닉스 탄생…SK하닉 장중 7%대 급등[줍줍리포트]</t>
+          <t>'10만전자·60만닉스' 랠리…홍콩 레버리지 ETF로 돈 몰린다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가가 장 중 7% 넘게 상승하며 60만 원 돌파에 성공했다. 3일 한국거래소에 따르면 이날 오전 10시 23분 현재 SK..</t>
+          <t>삼성전자와 SK하이닉스가 나란히 사상 최고가를 경신하며 고공행진을 이어가는 가운데, 이들 종목을 기초자산으로 한 해외 레버리지 상장지수..</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>뉴시스</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-11-03 10:35:10</t>
+          <t>2025-11-03 10:54:44</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551133</t>
+          <t>https://n.news.naver.com/mnews/article/003/0013576788</t>
         </is>
       </c>
     </row>
@@ -881,27 +881,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>367조 '토큰증권'시장 정조준… '조각투자' 플랫폼 최종선정 관건은</t>
+          <t>사상 최초 ‘60만닉스’ 터치…‘엔비디아 동맹’ 韓 AI 대표주 ‘불기둥’ [투자360]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2030년 최대 367조원 규모의 시장으로 평가 받는 미래 토큰증권(STO) 시장 선점을 위한 조각투자 장외거래소(유통플랫폼) 예비인가..</t>
+          <t>이재명 대통령이 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자 접견에 앞서 국내 기업 대표들과 함께 기..</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-11-03 10:21:49</t>
+          <t>2025-11-03 10:46:19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110803</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551595</t>
         </is>
       </c>
     </row>
@@ -911,27 +911,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>현대오토에버 ‘엔비디아 AI 동맹’ 수혜 기대에 급등 [종목Pick]</t>
+          <t>"젠슨 황 엔비디아 CEO, 10억달러 자사주 현금화"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>이재명 대통령이 지난달 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자(CEO) 접견 전 과학기술정보통신..</t>
+          <t>인공지능(AI) 붐과 함께 승승장구 중인 엔비디아의 젠슨 황 최고경영자(CEO)가 지난 6월 이후 10억달러가 넘는 자사주를 현금화했다..</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-03 10:19:10</t>
+          <t>2025-11-03 10:42:25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551565</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673522</t>
         </is>
       </c>
     </row>
@@ -941,27 +941,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>“시진핑 만나 기뻐” 박진영 소감에 한한령 해제 기대 ‘솔솔’…JYP 엔터 5%대 상승 [종목Pick]</t>
+          <t>사상 초유의 60만닉스 탄생…SK하닉 장중 7%대 급등[줍줍리포트]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JYP 엔터테인먼트 5.44% 오름세 기록 와이지엔터테인먼트 +0.66%·하이브 +0.29% 박 위원장 “양국 국민 더 가까워졌으면” ..</t>
+          <t>SK하이닉스 주가가 장 중 7% 넘게 상승하며 60만 원 돌파에 성공했다. 3일 한국거래소에 따르면 이날 오전 10시 23분 현재 SK..</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-03 10:17:15</t>
+          <t>2025-11-03 10:35:10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551564</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551133</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>광동제약 EB 철회 불똥...태광산업, 자사주 EB 고심</t>
+          <t>367조 '토큰증권'시장 정조준… '조각투자' 플랫폼 최종선정 관건은</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>광동제약의 자기주식 교환사채 발행 철회 불똥이 태광산업으로 번졌다. 태광산업의 자사주 EB 발행 규모가 발행주식총수의 24%에 달하는 ..</t>
+          <t>2030년 최대 367조원 규모의 시장으로 평가 받는 미래 토큰증권(STO) 시장 선점을 위한 조각투자 장외거래소(유통플랫폼) 예비인가..</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아이뉴스24</t>
+          <t>머니S</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-03 10:14:11</t>
+          <t>2025-11-03 10:21:49</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0000977292</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001110803</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>“삼전 수익률보다 높다”…‘15만전자·75만닉스’ 기대에 반도체 ETF로 몰리는 개미들 [투자360]</t>
+          <t>현대오토에버 ‘엔비디아 AI 동맹’ 수혜 기대에 급등 [종목Pick]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인 투자자 반도체 랠리 ‘확신 베팅’ 증권가도 삼전·SK하이닉스 목표주가 상향 일부 반도체 ETF, 개별종목 한달 수익률 추월 4분기..</t>
+          <t>이재명 대통령이 지난달 31일 APEC 정상회의장인 경주화백컨벤션센터에서 젠슨 황 엔비디아 최고경영자(CEO) 접견 전 과학기술정보통신..</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-03 10:01:09</t>
+          <t>2025-11-03 10:19:10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551534</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551565</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>현대차, 한달새 시총 15조 늘자 순위도 3계단 껑충…‘개미 랠리’ 속 목표가 36만원 등장 [투자360]</t>
+          <t>“시진핑 만나 기뻐” 박진영 소감에 한한령 해제 기대 ‘솔솔’…JYP 엔터 5%대 상승 [종목Pick]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>현대차, 한달새 시총 15조↑…한 달간 개인 1조4000억·기관 800억 순매수 거래대금 23배 폭증·신용비율 0.45까지 상승…‘개미..</t>
+          <t>JYP 엔터테인먼트 5.44% 오름세 기록 와이지엔터테인먼트 +0.66%·하이브 +0.29% 박 위원장 “양국 국민 더 가까워졌으면” ..</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-03 09:54:09</t>
+          <t>2025-11-03 10:17:15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551522</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551564</t>
         </is>
       </c>
     </row>
@@ -1061,27 +1061,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>‘연말 랠리’ 기대 꺾인 뉴욕증시…소비 둔화·셧다운·연준 경계 삼중 악재 [투자360]</t>
+          <t>광동제약 EB 철회 불똥...태광산업, 자사주 EB 고심</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1950년 이후 11월 평균 수익률 1.82%, 12월 1.49% ‘강세 구간’ 올해는 소비 5.3% 감소·셧다운 장기화로 연말 소비 ..</t>
+          <t>광동제약의 자기주식 교환사채 발행 철회 불똥이 태광산업으로 번졌다. 태광산업의 자사주 EB 발행 규모가 발행주식총수의 24%에 달하는 ..</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>아이뉴스24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-03 09:51:15</t>
+          <t>2025-11-03 10:14:11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551518</t>
+          <t>https://n.news.naver.com/mnews/article/031/0000977292</t>
         </is>
       </c>
     </row>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'월요병'이 낫네…코스피, 개인 7000억 순매수에 4160선까지 치솟아[마켓시그널]</t>
+          <t>“삼전 수익률보다 높다”…‘15만전자·75만닉스’ 기대에 반도체 ETF로 몰리는 개미들 [투자360]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>코스피 지수가 전인미답의 ‘사천피’ 달성 이후에도 숨 고르기 장세 없이 고공 행진 중이다. 상장 기업들의 실적 발표를 앞두고 호실적이 ..</t>
+          <t>개인 투자자 반도체 랠리 ‘확신 베팅’ 증권가도 삼전·SK하이닉스 목표주가 상향 일부 반도체 ETF, 개별종목 한달 수익률 추월 4분기..</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-03 09:48:10</t>
+          <t>2025-11-03 10:01:09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551090</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551534</t>
         </is>
       </c>
     </row>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"4150선 돌파"…코스피, 개인 '사자'에 사상 최고치 또 경신</t>
+          <t>현대차, 한달새 시총 15조 늘자 순위도 3계단 껑충…‘개미 랠리’ 속 목표가 36만원 등장 [투자360]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>원·달러 환율 3.8원 오른 1428.2원 코스피가 개인들의 매수세에 힘입어 상승 출발하면서 또다시 사상 최고치를 경신했다. 3일 한국..</t>
+          <t>현대차, 한달새 시총 15조↑…한 달간 개인 1조4000억·기관 800억 순매수 거래대금 23배 폭증·신용비율 0.45까지 상승…‘개미..</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>더팩트</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-03 09:44:17</t>
+          <t>2025-11-03 09:54:09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000439809</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551522</t>
         </is>
       </c>
     </row>
@@ -1151,27 +1151,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>두나무·빗썸에 ‘금융사’ 잣대 들이댄 공정위 vs 금융위 “가상자산은 금융 아냐”</t>
+          <t>‘연말 랠리’ 기대 꺾인 뉴욕증시…소비 둔화·셧다운·연준 경계 삼중 악재 [투자360]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>공정위 ‘두나무·빗썸 금융복합그룹 지정’ 추진 ‘금가분리’ 원칙과 정면충돌…정책 딜레마 주력사업은 ‘비금융’, 그룹은 ‘금융’(?) 법..</t>
+          <t>1950년 이후 11월 평균 수익률 1.82%, 12월 1.49% ‘강세 구간’ 올해는 소비 5.3% 감소·셧다운 장기화로 연말 소비 ..</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-03 09:42:05</t>
+          <t>2025-11-03 09:51:15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583414</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551518</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"中, 미 조선·해운 보복 철회"…한화오션 3%대 강세</t>
+          <t>'월요병'이 낫네…코스피, 개인 7000억 순매수에 4160선까지 치솟아[마켓시그널]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화오션 주가가 3일 장 초반 강세다. 중국이 한화오션의 미국 자회사에 부과한 제재가 풀릴 가능성이 제기되면서다. 이날 오전 9시27분..</t>
+          <t>코스피 지수가 전인미답의 ‘사천피’ 달성 이후에도 숨 고르기 장세 없이 고공 행진 중이다. 상장 기업들의 실적 발표를 앞두고 호실적이 ..</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-03 09:39:14</t>
+          <t>2025-11-03 09:48:10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205931</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551090</t>
         </is>
       </c>
     </row>
@@ -1211,27 +1211,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>증권가 "내년엔 '오천피' 간다…정상화 넘어 '코리아프리미엄' 국면 진입"</t>
+          <t>"4150선 돌파"…코스피, 개인 '사자'에 사상 최고치 또 경신</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>국내 증권사들이 내년 코스피 지수 상단을 최고 5000포인트까지 줄줄이 상향했다. 코리아디스카운트 해소를 넘어 프리미엄 국면에 진입할 ..</t>
+          <t>원·달러 환율 3.8원 오른 1428.2원 코스피가 개인들의 매수세에 힘입어 상승 출발하면서 또다시 사상 최고치를 경신했다. 3일 한국..</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>더팩트</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-11-03 09:34:13</t>
+          <t>2025-11-03 09:44:17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580759</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000439809</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1241,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>반도체·2차전지 빼고 전부 ‘왕따’…코스피 상승률 못 따라가는 KRX 업종 지수 [투자360]</t>
+          <t>두나무·빗썸에 ‘금융사’ 잣대 들이댄 공정위 vs 금융위 “가상자산은 금융 아냐”</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KRX 35개 지수 가운데 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 [챗GPT를 사용해..</t>
+          <t>공정위 ‘두나무·빗썸 금융복합그룹 지정’ 추진 ‘금가분리’ 원칙과 정면충돌…정책 딜레마 주력사업은 ‘비금융’, 그룹은 ‘금융’(?) 법..</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11-03 09:31:12</t>
+          <t>2025-11-03 09:42:05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551479</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583414</t>
         </is>
       </c>
     </row>
@@ -1271,27 +1271,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스테이블코인, '외국환'으로 묶이나… 규제냐 제도권 편입이냐 기로에 선 시장</t>
+          <t>"中, 미 조선·해운 보복 철회"…한화오션 3%대 강세</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>스테이블코인을 '외국환'으로 규제하려는 입법 논의가 본격화하면서, 그 법적 지위를 둘러싼 논쟁이 국내 디지털 금융 정책의 핵심 변수로 ..</t>
+          <t>한화오션 주가가 3일 장 초반 강세다. 중국이 한화오션의 미국 자회사에 부과한 제재가 풀릴 가능성이 제기되면서다. 이날 오전 9시27분..</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-11-03 09:30:09</t>
+          <t>2025-11-03 09:39:14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087382</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205931</t>
         </is>
       </c>
     </row>
@@ -1301,27 +1301,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>숨고르기 없는 코스피…'4200피' 향해 질주</t>
+          <t>증권가 "내년엔 '오천피' 간다…정상화 넘어 '코리아프리미엄' 국면 진입"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>역사상 최고치를 연일 갱신 중인 코스피가 ‘4200선’을 향해 달려가고 있다. 코스피가 상승 출발해 4130대를 나타낸 3일 오전 서울..</t>
+          <t>국내 증권사들이 내년 코스피 지수 상단을 최고 5000포인트까지 줄줄이 상향했다. 코리아디스카운트 해소를 넘어 프리미엄 국면에 진입할 ..</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-11-03 09:22:14</t>
+          <t>2025-11-03 09:34:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154477</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580759</t>
         </is>
       </c>
     </row>
@@ -1331,27 +1331,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코스피, 4200 등반 시도…HD현대중공업·한화오션 3%대 강세</t>
+          <t>반도체·2차전지 빼고 전부 ‘왕따’…코스피 상승률 못 따라가는 KRX 업종 지수 [투자360]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>지난주 ‘슈퍼위크’를 소화한 코스피가 3일 또 한번 강세로 장을 시작했다. 한국거래소에 따르면 코스피는 전장보다 15.86포인트(0.3..</t>
+          <t>KRX 35개 지수 가운데 24개가 뒤쳐져 반도체·정유화학·2차전지 빼고 부진 내수·필수소비재는 ‘마이너스’ 수익률 [챗GPT를 사용해..</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-03 09:13:22</t>
+          <t>2025-11-03 09:31:12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991048</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551479</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>코스피, 장중 또 사상 최고치 경신…4160선 위로</t>
+          <t>스테이블코인, '외국환'으로 묶이나… 규제냐 제도권 편입이냐 기로에 선 시장</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>코스피지수가 3일 장 초반 1% 넘게 올라 장중 기준 사상 최고치를 재차 경신했다. 엔비디아가 한국 정부와 기업에 인공지능(AI) 칩 ..</t>
+          <t>스테이블코인을 '외국환'으로 규제하려는 입법 논의가 본격화하면서, 그 법적 지위를 둘러싼 논쟁이 국내 디지털 금융 정책의 핵심 변수로 ..</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-11-03 09:11:12</t>
+          <t>2025-11-03 09:30:09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205888</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087382</t>
         </is>
       </c>
     </row>
@@ -1391,27 +1391,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코스피 4150선도 돌파…코스닥도 상승 출발</t>
+          <t>숨고르기 없는 코스피…'4200피' 향해 질주</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>코스피 지수가 3일 사상 최고치를 다시 경신하며 출발했다. 이날 오전 9시 16분 기준 코스피 지수는 전 거래일 대비 48.74포인트(..</t>
+          <t>역사상 최고치를 연일 갱신 중인 코스피가 ‘4200선’을 향해 달려가고 있다. 코스피가 상승 출발해 4130대를 나타낸 3일 오전 서울..</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-11-03 09:03:08</t>
+          <t>2025-11-03 09:22:14</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119582</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154477</t>
         </is>
       </c>
     </row>
@@ -1421,27 +1421,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LG화학, 업황개선·LG엔솔 지분활용 주목…목표가 35%↑</t>
+          <t>코스피, 4200 등반 시도…HD현대중공업·한화오션 3%대 강세</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>iM증권이 3일 LG화학에 대한 목표주가를 기존 대비 35% 높은 50만원으로 상향했다. 내년 업황 회복과 LG에너지솔루션 지분활용 의..</t>
+          <t>지난주 ‘슈퍼위크’를 소화한 코스피가 3일 또 한번 강세로 장을 시작했다. 한국거래소에 따르면 코스피는 전장보다 15.86포인트(0.3..</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>디지털타임스</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:23</t>
+          <t>2025-11-03 09:13:22</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272276</t>
+          <t>https://n.news.naver.com/mnews/article/029/0002991048</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"사모펀드 규제? 국내 자본시장 죽일 것"</t>
+          <t>코스피, 장중 또 사상 최고치 경신…4160선 위로</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MBK파트너스의 홈플러스 사태를 계기로 정치권과 금융당국 내부에서 사모펀드(PE)의 기업 지배권 관련 규제가 필요하다는 목소리가 커지고..</t>
+          <t>코스피지수가 3일 장 초반 1% 넘게 올라 장중 기준 사상 최고치를 재차 경신했다. 엔비디아가 한국 정부와 기업에 인공지능(AI) 칩 ..</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:09</t>
+          <t>2025-11-03 09:11:12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087377</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205888</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ETF 배당금도 분리과세 될까...관건은 '배당성향' 요건</t>
+          <t>코스피 4150선도 돌파…코스닥도 상승 출발</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>고배당주에 투자하는 ETF 분배금(배당금)은 왜 분리과세 안 해주나요" 배당소득의 분리과세방안이 국회에서 논의중인 가운데 고배당 기업들..</t>
+          <t>코스피 지수가 3일 사상 최고치를 다시 경신하며 출발했다. 이날 오전 9시 16분 기준 코스피 지수는 전 거래일 대비 48.74포인트(..</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:09</t>
+          <t>2025-11-03 09:03:08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041354</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119582</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>내 속만 타들어 가네…코스피 불 뿜는데 '코스닥 3000 시대' 언제 오나</t>
+          <t>LG화학, 업황개선·LG엔솔 지분활용 주목…목표가 35%↑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
+          <t>iM증권이 3일 LG화학에 대한 목표주가를 기존 대비 35% 높은 50만원으로 상향했다. 내년 업황 회복과 LG에너지솔루션 지분활용 의..</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-11-03 09:00:00</t>
+          <t>2025-11-03 09:00:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272275</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272276</t>
         </is>
       </c>
     </row>
@@ -1541,27 +1541,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>성장축 올라탄 종목은 따로 있다… 네 전문가가 밝힌 ‘현재 최우선 체크 종목’[진짜 주식 3부]</t>
+          <t>"사모펀드 규제? 국내 자본시장 죽일 것"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>지난 10월 31일(금) 방송된 한국경제TV ‘진짜 주식 3부’에서는 신학수 전문가(MJ스탁), 한중연 전문가(에스엠티엠 컨설팅), 전..</t>
+          <t>MBK파트너스의 홈플러스 사태를 계기로 정치권과 금융당국 내부에서 사모펀드(PE)의 기업 지배권 관련 규제가 필요하다는 목소리가 커지고..</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-11-03 08:56:10</t>
+          <t>2025-11-03 09:00:09</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229280</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087377</t>
         </is>
       </c>
     </row>
@@ -1571,27 +1571,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>“순금에 이자가 붙는다고?”…‘하나골드신탁’ 연일 매진</t>
+          <t>ETF 배당금도 분리과세 될까...관건은 '배당성향' 요건</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>‘장롱금’ 140조 깨운다 ‘금 신탁’, 90분만에 40억 ‘완판’ 순금 100g 이상 맡기면 1.5% 이자 고액 자산가 증여 수단으로..</t>
+          <t>고배당주에 투자하는 ETF 분배금(배당금)은 왜 분리과세 안 해주나요" 배당소득의 분리과세방안이 국회에서 논의중인 가운데 고배당 기업들..</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-11-03 08:53:08</t>
+          <t>2025-11-03 09:00:09</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583386</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041354</t>
         </is>
       </c>
     </row>
@@ -1601,27 +1601,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>“현금 쟁여놓은 버핏 속내가 궁금해”…버크셔, 올해 자사주 매입까지 중단</t>
+          <t>내 속만 타들어 가네…코스피 불 뿜는데 '코스닥 3000 시대' 언제 오나</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6개월새 주가 12% 떨어져도 매입 없어 버크셔 보유 현금 546조원 사상 최대치 투자자들 ‘미국 증시 고평가’ 신호로 해석 ‘투자의 ..</t>
+          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-11-03 08:52:08</t>
+          <t>2025-11-03 09:00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583385</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272275</t>
         </is>
       </c>
     </row>
@@ -1631,27 +1631,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>한화시스템, 해외 기업도 찾는 K-방산 부품…목표가 11.7% 상향-iM</t>
+          <t>성장축 올라탄 종목은 따로 있다… 네 전문가가 밝힌 ‘현재 최우선 체크 종목’[진짜 주식 3부]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>급증하는 글로벌 방산 수요로 국내 방산 반체계/부품 업체를 찾는 해외 방산기업이 늘면서 한화시스템 수주가 증가할 것이라는 전망이 나왔다..</t>
+          <t>지난 10월 31일(금) 방송된 한국경제TV ‘진짜 주식 3부’에서는 신학수 전문가(MJ스탁), 한중연 전문가(에스엠티엠 컨설팅), 전..</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-11-03 08:39:09</t>
+          <t>2025-11-03 08:56:10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272256</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229280</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>관세부담 덜어낸 현대차...증권가 “주가 20% 이상 상승여력” [오늘 나온 보고서]</t>
+          <t>“순금에 이자가 붙는다고?”…‘하나골드신탁’ 연일 매진</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>美 자동차 관세 25%→15% 4분기 팰리세이드 출시하며 미국 시장서 ‘골든 사이클’시작 증권사들이 현대자동차 목표 주가를 31만원에서..</t>
+          <t>‘장롱금’ 140조 깨운다 ‘금 신탁’, 90분만에 40억 ‘완판’ 순금 100g 이상 맡기면 1.5% 이자 고액 자산가 증여 수단으로..</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-11-03 08:38:08</t>
+          <t>2025-11-03 08:53:08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/009/0005583377</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583386</t>
         </is>
       </c>
     </row>
@@ -1691,27 +1691,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>젠슨 황과 '깐부 회동'에 삼성전자·네이버, 프리마켓서 강세</t>
+          <t>“현금 쟁여놓은 버핏 속내가 궁금해”…버크셔, 올해 자사주 매입까지 중단</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>삼성전자(005930)와 네이버(035420), 현대차(005380) 등 이른바 '깐부 회동' 수혜주가 넥스트레이드 프리마켓(오전 8시..</t>
+          <t>6개월새 주가 12% 떨어져도 매입 없어 버크셔 보유 현금 546조원 사상 최대치 투자자들 ‘미국 증시 고평가’ 신호로 해석 ‘투자의 ..</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-03 08:38:02</t>
+          <t>2025-11-03 08:52:08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580543</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583385</t>
         </is>
       </c>
     </row>
@@ -1721,27 +1721,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>이재용·젠슨황 치맥 회동…증권가 '삼성·엔비디아 AI동맹 가시화'</t>
+          <t>한화시스템, 해외 기업도 찾는 K-방산 부품…목표가 11.7% 상향-iM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15년 만에 한국을 방문한 인공지능(AI) 반도체 기업 엔비디아의 최고경영자(CEO) 젠슨 황이 이재용 삼성전자 회장과 치맥 회동을 통..</t>
+          <t>급증하는 글로벌 방산 수요로 국내 방산 반체계/부품 업체를 찾는 해외 방산기업이 늘면서 한화시스템 수주가 증가할 것이라는 전망이 나왔다..</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-11-03 08:36:08</t>
+          <t>2025-11-03 08:39:09</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041353</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272256</t>
         </is>
       </c>
     </row>
@@ -1751,27 +1751,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한국투자證 “풍산, 회복 가능한 어닝 쇼크… 목표가는 하향”</t>
+          <t>관세부담 덜어낸 현대차...증권가 “주가 20% 이상 상승여력” [오늘 나온 보고서]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국투자증권은 풍산에 대해 회복 가능한 어닝쇼크를 기록해 투자 포인트는 전혀 훼손되지 않았다고 3일 평했다. 그러면서 투자의견 ‘매수(..</t>
+          <t>美 자동차 관세 25%→15% 4분기 팰리세이드 출시하며 미국 시장서 ‘골든 사이클’시작 증권사들이 현대자동차 목표 주가를 31만원에서..</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-11-03 08:34:11</t>
+          <t>2025-11-03 08:38:08</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119572</t>
+          <t>https://n.news.naver.com/mnews/article/009/0005583377</t>
         </is>
       </c>
     </row>
@@ -1781,27 +1781,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LS증권 "한화시스템 필리조선소 적자에도 목표가 8% 상향"[아침밥]</t>
+          <t>젠슨 황과 '깐부 회동'에 삼성전자·네이버, 프리마켓서 강세</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>머니S 증권전문기자들이 매일 아침 쏟아지는 증권사 리포트 중에서 가장 알찬 리포트의 핵심을 요약해 제공하는 '아침밥'을 통해 든든하게 ..</t>
+          <t>삼성전자(005930)와 네이버(035420), 현대차(005380) 등 이른바 '깐부 회동' 수혜주가 넥스트레이드 프리마켓(오전 8시..</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-11-03 08:33:07</t>
+          <t>2025-11-03 08:38:02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110730</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580543</t>
         </is>
       </c>
     </row>
@@ -1811,27 +1811,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>부동산 막히자 빨라진 ‘머니무브’…예금 빼서 증시로 [투자360]</t>
+          <t>이재용·젠슨황 치맥 회동…증권가 '삼성·엔비디아 AI동맹 가시화'</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>증시 사천피 불장에 자금 폭주 증시 대기자금 85조 ‘역대 최대’ 개인 매수세 확대 속 은행은 단기자금 이탈 지난달 12일 서울 시내의..</t>
+          <t>15년 만에 한국을 방문한 인공지능(AI) 반도체 기업 엔비디아의 최고경영자(CEO) 젠슨 황이 이재용 삼성전자 회장과 치맥 회동을 통..</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-11-03 08:30:11</t>
+          <t>2025-11-03 08:36:08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551397</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041353</t>
         </is>
       </c>
     </row>
@@ -1841,27 +1841,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>연준, 매파적 기조 확산 - [굿모닝 글로벌 이슈]</t>
+          <t>한국투자證 “풍산, 회복 가능한 어닝 쇼크… 목표가는 하향”</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>전일장 아마존의 호실적이 증시를 이끌며 반등했지만 연준 위원들의 매파적인 발언에 상승폭은 제한적이었습니다. 먼저, 지난 회의에서 ‘금리..</t>
+          <t>한국투자증권은 풍산에 대해 회복 가능한 어닝쇼크를 기록해 투자 포인트는 전혀 훼손되지 않았다고 3일 평했다. 그러면서 투자의견 ‘매수(..</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-11-03 08:30:08</t>
+          <t>2025-11-03 08:34:11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229272</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119572</t>
         </is>
       </c>
     </row>
@@ -1871,27 +1871,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>국내외 불장에 정책 모멘텀까지…하나證 "증권株, 더 달린다"[마켓시그널]</t>
+          <t>LS증권 "한화시스템 필리조선소 적자에도 목표가 8% 상향"[아침밥]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>지난달 국내 증시의 일평균 거래대금이 2021년 1월 이후 최고치를 기록하고, 해외 주식 거래 규모마저 역대 최대치를 갈아치우면서 증권..</t>
+          <t>머니S 증권전문기자들이 매일 아침 쏟아지는 증권사 리포트 중에서 가장 알찬 리포트의 핵심을 요약해 제공하는 '아침밥'을 통해 든든하게 ..</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>머니S</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-11-03 08:29:09</t>
+          <t>2025-11-03 08:33:07</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004551016</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001110730</t>
         </is>
       </c>
     </row>
@@ -1901,27 +1901,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>역사적 10월 후 '모멘텀 진공' 들어선 코스피…단기 변동성 확대 [오늘장 미리보기]</t>
+          <t>부동산 막히자 빨라진 ‘머니무브’…예금 빼서 증시로 [투자360]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>코스피지수가 4100포인트를 돌파하며 역사에 남을 10월을 마무리 한 가운데 11월 시장은 '모멘텀 진공상태'에 진입할 것이란 전망이 ..</t>
+          <t>증시 사천피 불장에 자금 폭주 증시 대기자금 85조 ‘역대 최대’ 개인 매수세 확대 속 은행은 단기자금 이탈 지난달 12일 서울 시내의..</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-11-03 08:25:11</t>
+          <t>2025-11-03 08:30:11</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205861</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551397</t>
         </is>
       </c>
     </row>
@@ -1931,27 +1931,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iM證 “삼성물산, 원전·바이오·지배구조 개편 삼박자로 가치 성장 가속화”</t>
+          <t>연준, 매파적 기조 확산 - [굿모닝 글로벌 이슈]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>iM증권은 3일 삼성물산에 대해 원전, 바이오, 지배구조 개편 등으로 가치 성장이 가속화될 것이라고 전망했다. 목표 주가는 기존 18만..</t>
+          <t>전일장 아마존의 호실적이 증시를 이끌며 반등했지만 연준 위원들의 매파적인 발언에 상승폭은 제한적이었습니다. 먼저, 지난 회의에서 ‘금리..</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-11-03 08:23:08</t>
+          <t>2025-11-03 08:30:08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119570</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229272</t>
         </is>
       </c>
     </row>
@@ -1961,27 +1961,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"필리조선소, 핵잠 건조 조선소로 확장…한화시스템 목표가↑"-NH</t>
+          <t>국내외 불장에 정책 모멘텀까지…하나證 "증권株, 더 달린다"[마켓시그널]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 한화시스템의 목표주가를 6만8500원에서 7만3000원으로 높였다. 필리조선소가 향후 핵잠수함 건조로 업그레이드돼 ..</t>
+          <t>지난달 국내 증시의 일평균 거래대금이 2021년 1월 이후 최고치를 기록하고, 해외 주식 거래 규모마저 역대 최대치를 갈아치우면서 증권..</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-11-03 08:19:11</t>
+          <t>2025-11-03 08:29:09</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205859</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004551016</t>
         </is>
       </c>
     </row>
@@ -1991,27 +1991,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"역대급으로 돈 잘 굴렸다"…'1300조 덩치가 최강 전략' 국민연금, 깜짝 등판한 곳[기금·공제 대해부]①</t>
+          <t>역사적 10월 후 '모멘텀 진공' 들어선 코스피…단기 변동성 확대 [오늘장 미리보기]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>편집자주연기금과 공제회가 자본시장의 핵심 플레이어로 자리매김한 지 오래다. 연기금과 공제회는 국민의 노후보장(연기금)과 회원들의 자산증..</t>
+          <t>코스피지수가 4100포인트를 돌파하며 역사에 남을 10월을 마무리 한 가운데 11월 시장은 '모멘텀 진공상태'에 진입할 것이란 전망이 ..</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-11-03 08:16:53</t>
+          <t>2025-11-03 08:25:11</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673330</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205861</t>
         </is>
       </c>
     </row>
@@ -2021,27 +2021,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>방산도 다 잘나가는 것 아니네…“풍산 목표가 19.3만→16만 ‘하향’”</t>
+          <t>iM證 “삼성물산, 원전·바이오·지배구조 개편 삼박자로 가치 성장 가속화”</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 풍산의 3분기 실적이 가이던스를 하회했으며 수익성 전망도 낮아 목표주가를 19만3000원에서 16만원으로 낮춰 잡았..</t>
+          <t>iM증권은 3일 삼성물산에 대해 원전, 바이오, 지배구조 개편 등으로 가치 성장이 가속화될 것이라고 전망했다. 목표 주가는 기존 18만..</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-11-03 08:13:53</t>
+          <t>2025-11-03 08:23:08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991024</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119570</t>
         </is>
       </c>
     </row>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>달러 강세와 증시 조정…환율 1430원대 안착[외환브리핑]</t>
+          <t>"필리조선소, 핵잠 건조 조선소로 확장…한화시스템 목표가↑"-NH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>원·달러 환율은 1430원대에서 안착을 시도할 것으로 전망된다. 글로벌 달러화 강세 압박이 재개하고, 고점 논란이 부상한 성장주 위험선..</t>
+          <t>NH투자증권은 3일 한화시스템의 목표주가를 6만8500원에서 7만3000원으로 높였다. 필리조선소가 향후 핵잠수함 건조로 업그레이드돼 ..</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-11-03 08:13:09</t>
+          <t>2025-11-03 08:19:11</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154351</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205859</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>기아, 피지컬AI 본격화로 밸류 높아진다[클릭e종목]</t>
+          <t>"역대급으로 돈 잘 굴렸다"…'1300조 덩치가 최강 전략' 국민연금, 깜짝 등판한 곳[기금·공제 대해부]①</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3일 삼성증권은 기아에 대해 관세 불확실성 제거로 일본 경쟁사와 동등한 경쟁이 가능해졌고, 엔비디아와 협력으로 피지컬(Physical)..</t>
+          <t>편집자주연기금과 공제회가 자본시장의 핵심 플레이어로 자리매김한 지 오래다. 연기금과 공제회는 국민의 노후보장(연기금)과 회원들의 자산증..</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-11-03 08:08:07</t>
+          <t>2025-11-03 08:16:53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673324</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673330</t>
         </is>
       </c>
     </row>
@@ -2111,27 +2111,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>‘업토버’ 깨진 비트코인 11만달러 박스권…ETF 자금유출 [투자360]</t>
+          <t>방산도 다 잘나가는 것 아니네…“풍산 목표가 19.3만→16만 ‘하향’”</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>비트코인 이달 11만달러 전후 흐름 현물 ETF서 3거래일째 순매도세 [헤럴드경제=유동현 기자] ‘업토버(Uptober·10월 상승장)..</t>
+          <t>NH투자증권은 3일 풍산의 3분기 실적이 가이던스를 하회했으며 수익성 전망도 낮아 목표주가를 19만3000원에서 16만원으로 낮춰 잡았..</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>디지털타임스</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-11-03 08:07:11</t>
+          <t>2025-11-03 08:13:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551385</t>
+          <t>https://n.news.naver.com/mnews/article/029/0002991024</t>
         </is>
       </c>
     </row>
@@ -2141,27 +2141,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>트럼프 관세 운명, 美 대법으로…AMD·팔란티어 실적에 AI 낙관론도 시험대[글로벌마켓레이더]</t>
+          <t>달러 강세와 증시 조정…환율 1430원대 안착[외환브리핑]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>美 대법, 보복성 관세 위헌 여부 구두심리 셧다운 장기화 속 경기 부담 확대 전망 AMD·팔란티어 실적 발표 [로이터] [헤럴드경제=문..</t>
+          <t>원·달러 환율은 1430원대에서 안착을 시도할 것으로 전망된다. 글로벌 달러화 강세 압박이 재개하고, 고점 논란이 부상한 성장주 위험선..</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-11-03 08:07:08</t>
+          <t>2025-11-03 08:13:09</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551384</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154351</t>
         </is>
       </c>
     </row>
@@ -2171,27 +2171,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"버핏의 버크셔가 이럴리 없는데"…美주식 고평가 신호?[뉴스새벽배송]</t>
+          <t>기아, 피지컬AI 본격화로 밸류 높아진다[클릭e종목]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>‘투자의 귀재’ 워런 버핏 회장(사진)이 이끄는 버크셔 해서웨이(이하 버크셔)가 최근 주가 부진에도 불구하고 자사주를 전혀 매입하지 않..</t>
+          <t>3일 삼성증권은 기아에 대해 관세 불확실성 제거로 일본 경쟁사와 동등한 경쟁이 가능해졌고, 엔비디아와 협력으로 피지컬(Physical)..</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-03 08:05:13</t>
+          <t>2025-11-03 08:08:07</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154343</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673324</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2201,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'슈퍼위크' 소화한 코스피 상승세 이어갈까…실적 관건[마켓뷰]</t>
+          <t>‘업토버’ 깨진 비트코인 11만달러 박스권…ETF 자금유출 [투자360]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>지난주 말 4,100선 첫 돌파…뉴욕증시도 3대 지수 강세 마감 '조·방·원' 실적 주시…단기 고점 부담에 '숨 고르기' 가능성도 아시..</t>
+          <t>비트코인 이달 11만달러 전후 흐름 현물 ETF서 3거래일째 순매도세 [헤럴드경제=유동현 기자] ‘업토버(Uptober·10월 상승장)..</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-03 08:04:12</t>
+          <t>2025-11-03 08:07:11</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0015719720</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551385</t>
         </is>
       </c>
     </row>
@@ -2231,27 +2231,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>신한 이수구, 누적 수익률 31%로 1위…효자 종목은 '두산'[스타워즈]</t>
+          <t>트럼프 관세 운명, 美 대법으로…AMD·팔란티어 실적에 AI 낙관론도 시험대[글로벌마켓레이더]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>'2025 한경스타워즈 실전투자대회(하반기)' 6주차 신한투자증권의 이수구 대구금융센터 대리가 직전주에 이어 1위를 차지했다. 인공지능..</t>
+          <t>美 대법, 보복성 관세 위헌 여부 구두심리 셧다운 장기화 속 경기 부담 확대 전망 AMD·팔란티어 실적 발표 [로이터] [헤럴드경제=문..</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-11-03 08:01:15</t>
+          <t>2025-11-03 08:07:08</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205855</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551384</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>‘스팩 합병 상장’ 엔비알모션 “글로벌 베어링 선두 기업으로 도약”</t>
+          <t>"버핏의 버크셔가 이럴리 없는데"…美주식 고평가 신호?[뉴스새벽배송]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>“엔비알모션은 수십 년간 일본·독일 등 해외 수입에 의존해 온 베어링 부품 시장에서 자체 기술로 국산화를 이끌어온 기업입니다. 지금은 ..</t>
+          <t>‘투자의 귀재’ 워런 버핏 회장(사진)이 이끄는 버크셔 해서웨이(이하 버크셔)가 최근 주가 부진에도 불구하고 자사주를 전혀 매입하지 않..</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-03 08:01:09</t>
+          <t>2025-11-03 08:05:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154337</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154343</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>"이젠 우리 차례"…반도체·방산 중기, 'ABCD' 특례로 코스닥 간다</t>
+          <t>'슈퍼위크' 소화한 코스피 상승세 이어갈까…실적 관건[마켓뷰]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
+          <t>지난주 말 4,100선 첫 돌파…뉴욕증시도 3대 지수 강세 마감 '조·방·원' 실적 주시…단기 고점 부담에 '숨 고르기' 가능성도 아시..</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-11-03 08:00:00</t>
+          <t>2025-11-03 08:04:12</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272246</t>
+          <t>https://n.news.naver.com/mnews/article/001/0015719720</t>
         </is>
       </c>
     </row>
@@ -2321,27 +2321,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>"LG화학, 내년 실적개선·LG엔솔 지분활용 기대"[클릭 e종목]</t>
+          <t>신한 이수구, 누적 수익률 31%로 1위…효자 종목은 '두산'[스타워즈]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>iM증권은 3일 LG화학에 대해 "내년 석유화학 업황 회복과 첨단소재 성장으로 실적 개선이 예상된다"며 투자의견 매수를 유지하고, 목표..</t>
+          <t>'2025 한경스타워즈 실전투자대회(하반기)' 6주차 신한투자증권의 이수구 대구금융센터 대리가 직전주에 이어 1위를 차지했다. 인공지능..</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-03 07:59:24</t>
+          <t>2025-11-03 08:01:15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673317</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205855</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>“필리조선소서 핵잠수함 건조”…한화시스템, 목표가 7%↑-NH</t>
+          <t>‘스팩 합병 상장’ 엔비알모션 “글로벌 베어링 선두 기업으로 도약”</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NH투자증권은 3일 한화시스템(272210)에 대해 필리조선소가 향후 핵잠수함 건조 가능 조선소로 성장할 것이라며 목표주가를 7만 30..</t>
+          <t>“엔비알모션은 수십 년간 일본·독일 등 해외 수입에 의존해 온 베어링 부품 시장에서 자체 기술로 국산화를 이끌어온 기업입니다. 지금은 ..</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-03 07:56:17</t>
+          <t>2025-11-03 08:01:09</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154333</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154337</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"SK이노베이션, 美 ESS 진출 고무적이나 아쉬운 규모"[클릭 e종목]</t>
+          <t>"이젠 우리 차례"…반도체·방산 중기, 'ABCD' 특례로 코스닥 간다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>iM증권은 3일 SK이노베이션의 목표주가를 14만8000원으로 상향했다. 다만, 국내 경쟁사들 대비 중장기 에너지저장장치(ESS) 설비..</t>
+          <t>내년이면 코스닥이 서른 살이 된다. 1996년 7월1일 미국 나스닥을 본떠 지수 1000을 기준으로 했지만 현재 출범 시점 지수에도 못..</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-03 07:55:53</t>
+          <t>2025-11-03 08:00:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673315</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005272246</t>
         </is>
       </c>
     </row>
@@ -2411,27 +2411,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LG전자, 1분기부터 반등 기대…목표가 16%↑-iM</t>
+          <t>"LG화학, 내년 실적개선·LG엔솔 지분활용 기대"[클릭 e종목]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>iM증권은 LG전자(066570)에 대해 4분기 부진한 실적을 기록한 뒤 2026년 1분기부터는 성수기와 경영 효율화 효과가 반영될 것..</t>
+          <t>iM증권은 3일 LG화학에 대해 "내년 석유화학 업황 회복과 첨단소재 성장으로 실적 개선이 예상된다"며 투자의견 매수를 유지하고, 목표..</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-03 07:52:15</t>
+          <t>2025-11-03 07:59:24</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154329</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673317</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LG화학, 실적 개선ㆍLGES 지분 활용 기대...목표주가 50만원↑-iM</t>
+          <t>“필리조선소서 핵잠수함 건조”…한화시스템, 목표가 7%↑-NH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>iM증권은 3일 LG화학(051910)에 대해 목표주가를 37만원에서 50만원으로 상향하고 투자의견 매수를 유지했다. 전유진 iM증권 ..</t>
+          <t>NH투자증권은 3일 한화시스템(272210)에 대해 필리조선소가 향후 핵잠수함 건조 가능 조선소로 성장할 것이라며 목표주가를 7만 30..</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-03 07:49:08</t>
+          <t>2025-11-03 07:56:17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154327</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154333</t>
         </is>
       </c>
     </row>
@@ -2471,27 +2471,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>"삼성전자, 엔비디아와 AI 동맹…메모리 사업 시너지 기대"-</t>
+          <t>"SK이노베이션, 美 ESS 진출 고무적이나 아쉬운 규모"[클릭 e종목]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KB증권은 3일 삼성전자에 대해 "엔비디아와의 세계 최대 인공지능(AI) 팩토리 구축 협력으로 메모리 사업의 시너지 효과가 기대된다"고..</t>
+          <t>iM증권은 3일 SK이노베이션의 목표주가를 14만8000원으로 상향했다. 다만, 국내 경쟁사들 대비 중장기 에너지저장장치(ESS) 설비..</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-03 07:46:16</t>
+          <t>2025-11-03 07:55:53</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205849</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673315</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5000피 향해 달리는 국장…외인들 '이 업종' 꽂혔다</t>
+          <t>LG전자, 1분기부터 반등 기대…목표가 16%↑-iM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>코스피 과열 부담에도 중장기적으로 우상향 기조를 유지하고, 이 가운데 주도 업종인 IT가 지수 상승을 견인할 것이라는 전망이 나왔다. ..</t>
+          <t>iM증권은 LG전자(066570)에 대해 4분기 부진한 실적을 기록한 뒤 2026년 1분기부터는 성수기와 경영 효율화 효과가 반영될 것..</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-11-03 07:45:08</t>
+          <t>2025-11-03 07:52:15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154325</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154329</t>
         </is>
       </c>
     </row>
@@ -2531,27 +2531,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>"GPU 26만장 확보로 AI 언어모델 및 서비스 개발 탄력"-하나</t>
+          <t>LG화학, 실적 개선ㆍLGES 지분 활용 기대...목표주가 50만원↑-iM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>하나증권은 3일 한국 정부와 기업이 엔비디아 그래픽카드(GPU) 26만장을 확보한 것과 관련해 "주요 산업에서 인공지능(AI) 개발과 ..</t>
+          <t>iM증권은 3일 LG화학(051910)에 대해 목표주가를 37만원에서 50만원으로 상향하고 투자의견 매수를 유지했다. 전유진 iM증권 ..</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-11-03 07:43:10</t>
+          <t>2025-11-03 07:49:08</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205848</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154327</t>
         </is>
       </c>
     </row>
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>삼성전자·엔비디아 협력에…KB證, “삼성에스디에스, 신규 사업 기회”</t>
+          <t>"삼성전자, 엔비디아와 AI 동맹…메모리 사업 시너지 기대"-</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KB증권은 3일 삼성에스디에스(삼성SDS)에 대해 삼성전자와 엔비디아가 구축하기로 한 인공지능(AI) 팩토리에 직접 관여된 실무 사업자..</t>
+          <t>KB증권은 3일 삼성전자에 대해 "엔비디아와의 세계 최대 인공지능(AI) 팩토리 구축 협력으로 메모리 사업의 시너지 효과가 기대된다"고..</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-03 07:42:09</t>
+          <t>2025-11-03 07:46:16</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119566</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205849</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>"한 주에 280만원 간다"…'황제주 중의 황제' 파격 전망</t>
+          <t>5000피 향해 달리는 국장…외인들 '이 업종' 꽂혔다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한국투자증권은 3일 효성중공업(298040)에 대해 글로벌 전력기기 업체 중 가장 빠르게, 가장 많이 성장하는 기업이라며 목표주가를 2..</t>
+          <t>코스피 과열 부담에도 중장기적으로 우상향 기조를 유지하고, 이 가운데 주도 업종인 IT가 지수 상승을 견인할 것이라는 전망이 나왔다. ..</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-03 07:39:08</t>
+          <t>2025-11-03 07:45:08</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154322</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154325</t>
         </is>
       </c>
     </row>
@@ -2621,27 +2621,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>기아, 4분기부터 반등 시작…목표가 11%↑-NH</t>
+          <t>"GPU 26만장 확보로 AI 언어모델 및 서비스 개발 탄력"-하나</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NH투자증권은 기아(000270)에 대해 4분기부터 본격적인 신차 출시 사이클에 돌입해 반등이 기대된다고 분석했다. 투자의견 ‘매수(B..</t>
+          <t>하나증권은 3일 한국 정부와 기업이 엔비디아 그래픽카드(GPU) 26만장을 확보한 것과 관련해 "주요 산업에서 인공지능(AI) 개발과 ..</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>이데일리</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-03 07:37:08</t>
+          <t>2025-11-03 07:43:10</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006154321</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205848</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한투證 “효성중공업, 美 매출 계속 성장할 것 …목표가 55%↑”</t>
+          <t>삼성전자·엔비디아 협력에…KB證, “삼성에스디에스, 신규 사업 기회”</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한국투자증권은 3일 효성중공업에 대해 미국 매출 비중이 계속 성장할 것이라며 목표 주가를 높여 잡았다. 투자 의견 ‘매수(Buy)’를 ..</t>
+          <t>KB증권은 3일 삼성에스디에스(삼성SDS)에 대해 삼성전자와 엔비디아가 구축하기로 한 인공지능(AI) 팩토리에 직접 관여된 실무 사업자..</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-11-03 07:25:07</t>
+          <t>2025-11-03 07:42:09</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119564</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119566</t>
         </is>
       </c>
     </row>
@@ -2681,27 +2681,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>심팩 최진식 중견련 회장, 홍영표 전 의원 무슨 관계?[거버넌스워치]</t>
+          <t>"한 주에 280만원 간다"…'황제주 중의 황제' 파격 전망</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>산업용 프레스 및 합금철을 주력으로 하는 중견그룹 심팩(SIMPAC)의 2대(代) 세습 작업이 재개됐다. 중견기업연합회 회장인 사주(社..</t>
+          <t>한국투자증권은 3일 효성중공업(298040)에 대해 글로벌 전력기기 업체 중 가장 빠르게, 가장 많이 성장하는 기업이라며 목표주가를 2..</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비즈워치</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-11-03 07:10:07</t>
+          <t>2025-11-03 07:39:08</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/648/0000041349</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154322</t>
         </is>
       </c>
     </row>
@@ -2711,27 +2711,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>"삼성전자, 더 오를 수 있다"…전문가 조언 들어보니 [인터뷰+]</t>
+          <t>기아, 4분기부터 반등 시작…목표가 11%↑-NH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>'한국에 투자할 종목이 많다'는 게 최근 글로벌 투자업계 관계자들의 반응입니다." 정성한 신한자산운용 주식투자운용본부장은 2일 한국경제..</t>
+          <t>NH투자증권은 기아(000270)에 대해 4분기부터 본격적인 신차 출시 사이클에 돌입해 반등이 기대된다고 분석했다. 투자의견 ‘매수(B..</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>이데일리</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-11-03 07:01:12</t>
+          <t>2025-11-03 07:37:08</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205840</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006154321</t>
         </is>
       </c>
     </row>
@@ -2741,27 +2741,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>위츠, GS와 손잡는다…“3년 내 전기차 충전기 매출 1000억”</t>
+          <t>한투證 “효성중공업, 美 매출 계속 성장할 것 …목표가 55%↑”</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>위츠, GS서 50억 투자 유치 미래 모빌리티 동맹 맺어 “GS차지비와 전기차 충전 협력 전기차 충전기 매출 1000억 목표” EV무선..</t>
+          <t>한국투자증권은 3일 효성중공업에 대해 미국 매출 비중이 계속 성장할 것이라며 목표 주가를 높여 잡았다. 투자 의견 ‘매수(Buy)’를 ..</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>한국경제</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-11-03 07:01:10</t>
+          <t>2025-11-03 07:25:07</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005205839</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119564</t>
         </is>
       </c>
     </row>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'드디어 관세 족쇄 풀었다'…'30만원 눈앞' 액셀 밟는 현대차 주가</t>
+          <t>심팩 최진식 중견련 회장, 홍영표 전 의원 무슨 관계?[거버넌스워치]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>현대차가 관세 우려 완화에 따라 주가 상승세가 이어지며 30만원 돌파를 눈앞에 뒀다. 3일 한국거래소에 따르면 현대차는 지난달 31일 ..</t>
+          <t>산업용 프레스 및 합금철을 주력으로 하는 중견그룹 심팩(SIMPAC)의 2대(代) 세습 작업이 재개됐다. 중견기업연합회 회장인 사주(社..</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>비즈워치</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-11-03 06:55:00</t>
+          <t>2025-11-03 07:10:07</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005673293</t>
+          <t>https://n.news.naver.com/mnews/article/648/0000041349</t>
         </is>
       </c>
     </row>
@@ -2801,27 +2801,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>국민연금, ‘오천피’에 ‘사상 최고’ 美 증시 타고 고갈 걱정 털어내나…주식 비중 50% 시대 개막 [투자360]</t>
+          <t>"삼성전자, 더 오를 수 있다"…전문가 조언 들어보니 [인터뷰+]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>‘안정’의 채권 줄이고 ‘수익’의 주식으로 1269조 ‘연금 고래’, 세계 시장으로 국내 증시 ‘과잉 영향력’ 해소 노후 자금 전략 대..</t>
+          <t>'한국에 투자할 종목이 많다'는 게 최근 글로벌 투자업계 관계자들의 반응입니다." 정성한 신한자산운용 주식투자운용본부장은 2일 한국경제..</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-11-03 06:48:09</t>
+          <t>2025-11-03 07:01:12</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551356</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205840</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>버핏이 볼 때 지금 주식 시장은 너무 고평가?…올해 자사주 매입 ‘제로’·현금 보유 ‘사상 최고 [투자360]</t>
+          <t>위츠, GS와 손잡는다…“3년 내 전기차 충전기 매출 1000억”</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6개월새 주가 12% 떨어졌는데 매입 없어 현금은 546조원 ‘사상최고’ 워런 버핏 버크셔해서웨이 회장. [AP·게티이미지뱅크] [헤럴..</t>
+          <t>위츠, GS서 50억 투자 유치 미래 모빌리티 동맹 맺어 “GS차지비와 전기차 충전 협력 전기차 충전기 매출 1000억 목표” EV무선..</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>한국경제</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-11-03 06:42:09</t>
+          <t>2025-11-03 07:01:10</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/016/0002551352</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005205839</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>"삼성전자, 지금이라도 사? 말아?"…'포모 vs 트라우마' 갈팡질팡 개미들</t>
+          <t>'드디어 관세 족쇄 풀었다'…'30만원 눈앞' 액셀 밟는 현대차 주가</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>삼성전자가 연일 사상 최고가를 경신하면서 개미투자자들은 "지금이라도 사야 한다"는 '포모(FOMO·나만 돈 못 번다는 공포)'와 "물리..</t>
+          <t>현대차가 관세 우려 완화에 따라 주가 상승세가 이어지며 30만원 돌파를 눈앞에 뒀다. 3일 한국거래소에 따르면 현대차는 지난달 31일 ..</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-11-03 06:40:00</t>
+          <t>2025-11-03 06:55:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580413</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005673293</t>
         </is>
       </c>
     </row>
@@ -2891,27 +2891,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>“주식하고 비교하면 아직 저렴” 쉬었던 금값 다시 꿈틀 [줍줍 리포트]</t>
+          <t>국민연금, ‘오천피’에 ‘사상 최고’ 美 증시 타고 고갈 걱정 털어내나…주식 비중 50% 시대 개막 [투자360]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한동안 사상 최고가를 연일 경신하다가 하락 전환 후 잠시 주춤했던 금값이 다시 오를 조짐을 보이고 있다. 전문가들은 일시적인 기술적 조..</t>
+          <t>‘안정’의 채권 줄이고 ‘수익’의 주식으로 1269조 ‘연금 고래’, 세계 시장으로 국내 증시 ‘과잉 영향력’ 해소 노후 자금 전략 대..</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-11-03 06:31:07</t>
+          <t>2025-11-03 06:48:09</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550980</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551356</t>
         </is>
       </c>
     </row>
@@ -2921,27 +2921,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>"사천피 넘어 4100까지 갈줄이야"…혼돈의 개미들, 다시 증시 '기웃'</t>
+          <t>버핏이 볼 때 지금 주식 시장은 너무 고평가?…올해 자사주 매입 ‘제로’·현금 보유 ‘사상 최고 [투자360]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>코스피가 '사천피' 달성 1주일도 안 돼 4100선까지 치솟았다. 중장기 상승세가 이어질 것이란 전망에 그간 증시를 관망하던 개인투자자..</t>
+          <t>6개월새 주가 12% 떨어졌는데 매입 없어 현금은 546조원 ‘사상최고’ 워런 버핏 버크셔해서웨이 회장. [AP·게티이미지뱅크] [헤럴..</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>뉴스1</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-11-03 06:20:00</t>
+          <t>2025-11-03 06:42:09</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008580403</t>
+          <t>https://n.news.naver.com/mnews/article/016/0002551352</t>
         </is>
       </c>
     </row>
@@ -2951,27 +2951,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'투자의 달인' 버핏 투자사, 중대 결정…'헉'</t>
+          <t>"삼성전자, 지금이라도 사? 말아?"…'포모 vs 트라우마' 갈팡질팡 개미들</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>'오마하의 현인'으로 불리는 워런 버핏(95) 회장의 버크셔 해서웨이(이하 버크셔)가 최근 자사주를 전혀 매입하지 않은 것으로 확인됐다..</t>
+          <t>삼성전자가 연일 사상 최고가를 경신하면서 개미투자자들은 "지금이라도 사야 한다"는 '포모(FOMO·나만 돈 못 번다는 공포)'와 "물리..</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>한국경제TV</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-11-03 06:16:55</t>
+          <t>2025-11-03 06:40:00</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/215/0001229262</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580413</t>
         </is>
       </c>
     </row>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>공시 위반 반복되는데… 깜깜이 주식 거래 막는 감시 시스템 없어</t>
+          <t>“주식하고 비교하면 아직 저렴” 쉬었던 금값 다시 꿈틀 [줍줍 리포트]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>주식 거래 자동 통보시스템 갖추고도 5%룰 위반 반복 본인과 특수관계인을 더해 발행 주식의 5% 이상을 보유한 주주에게 부여된 지분 공..</t>
+          <t>한동안 사상 최고가를 연일 경신하다가 하락 전환 후 잠시 주춤했던 금값이 다시 오를 조짐을 보이고 있다. 전문가들은 일시적인 기술적 조..</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>조선비즈</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-11-03 06:02:17</t>
+          <t>2025-11-03 06:31:07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/366/0001119555</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550980</t>
         </is>
       </c>
     </row>
@@ -3011,27 +3011,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>‘AI 경량화’ 노타 상장…‘아기상어’ 더핑크퐁컴퍼니 공모 [이런주 증시 캘린더]</t>
+          <t>"사천피 넘어 4100까지 갈줄이야"…혼돈의 개미들, 다시 증시 '기웃'</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>이번 주 국내 증시에서는 인공지능(AI) 기술 업체인 노타가 코스닥 시장에 상장한다. ‘아기상어’ 등으로 유명한 더핑크퐁컴퍼니는 상장을..</t>
+          <t>코스피가 '사천피' 달성 1주일도 안 돼 4100선까지 치솟았다. 중장기 상승세가 이어질 것이란 전망에 그간 증시를 관망하던 개인투자자..</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>뉴스1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:18</t>
+          <t>2025-11-03 06:20:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550977</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008580403</t>
         </is>
       </c>
     </row>
@@ -3041,27 +3041,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>"해외 금융기관들, 코스피 추가 상승 우세하다고 전망"</t>
+          <t>'투자의 달인' 버핏 투자사, 중대 결정…'헉'</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>코스피가 지난달 4000선을 돌파하면서 증권가에선 5000선을 넘보는 전망과 가격 부담에 대한 우려가 혼재한 상황이다. 그러나 대부분의..</t>
+          <t>'오마하의 현인'으로 불리는 워런 버핏(95) 회장의 버크셔 해서웨이(이하 버크셔)가 최근 자사주를 전혀 매입하지 않은 것으로 확인됐다..</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>파이낸셜뉴스</t>
+          <t>한국경제TV</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:14</t>
+          <t>2025-11-03 06:16:55</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/014/0005428360</t>
+          <t>https://n.news.naver.com/mnews/article/215/0001229262</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3071,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>쉬지 않고 내달린 코스피, 숨 고르기 할까…상승 모멘텀은 계속 [주간 증시 전망]</t>
+          <t>공시 위반 반복되는데… 깜깜이 주식 거래 막는 감시 시스템 없어</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>코스피 지수가 사상 최초로 4100선에 도달한 가운데 과열 부담을 해소하기 위해 한 차례 숨 고르기를 할 것이라는 전망이 나온다. 다만..</t>
+          <t>주식 거래 자동 통보시스템 갖추고도 5%룰 위반 반복 본인과 특수관계인을 더해 발행 주식의 5% 이상을 보유한 주주에게 부여된 지분 공..</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>서울경제</t>
+          <t>조선비즈</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-11-03 06:01:07</t>
+          <t>2025-11-03 06:02:17</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004550973</t>
+          <t>https://n.news.naver.com/mnews/article/366/0001119555</t>
         </is>
       </c>
     </row>
@@ -3101,27 +3101,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>‘사모펀드 대주주’ 법안 봇물...먹튀 사라질까</t>
+          <t>‘AI 경량화’ 노타 상장…‘아기상어’ 더핑크퐁컴퍼니 공모 [이런주 증시 캘린더]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>국내에서 사모펀드(PE)에 대한 인식은 대체로 좋지 않은 편이다. 지난 1997년 외환위기 직후 론스타 등 외국계 사모펀드들은 대기업 ..</t>
+          <t>이번 주 국내 증시에서는 인공지능(AI) 기술 업체인 노타가 코스닥 시장에 상장한다. ‘아기상어’ 등으로 유명한 더핑크퐁컴퍼니는 상장을..</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>이코노미스트</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-11-03 06:00:09</t>
+          <t>2025-11-03 06:01:18</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/243/0000087371</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550977</t>
         </is>
       </c>
     </row>
@@ -3131,27 +3131,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4100선 안착한 코스피, 숨고르기 구간 진입 “수익 방어할 때”</t>
+          <t>"해외 금융기관들, 코스피 추가 상승 우세하다고 전망"</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>코스피가 4100선을 지키며 상승 흐름을 이어갔다. 미국의 금리 인하와 미·중 정상회담 기대감, 반도체 업종의 호실적이 증시를 지탱한 ..</t>
+          <t>코스피가 지난달 4000선을 돌파하면서 증권가에선 5000선을 넘보는 전망과 가격 부담에 대한 우려가 혼재한 상황이다. 그러나 대부분의..</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>디지털타임스</t>
+          <t>파이낸셜뉴스</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-11-03 05:35:00</t>
+          <t>2025-11-03 06:01:14</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0002991013</t>
+          <t>https://n.news.naver.com/mnews/article/014/0005428360</t>
         </is>
       </c>
     </row>
@@ -3161,27 +3161,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>이제 첫 월급 받았는데 노후대비가 웬 말?… "TDF는 달라"</t>
+          <t>쉬지 않고 내달린 코스피, 숨 고르기 할까…상승 모멘텀은 계속 [주간 증시 전망]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>#1. 2025년 첫 직장을 구한 A씨(28)는 카드 명세서를 보고 고민에 빠졌다. 사회 진출이 남보다 늦은 만큼 모은 돈은 적은데 씀..</t>
+          <t>코스피 지수가 사상 최초로 4100선에 도달한 가운데 과열 부담을 해소하기 위해 한 차례 숨 고르기를 할 것이라는 전망이 나온다. 다만..</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>머니S</t>
+          <t>서울경제</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-11-03 05:00:00</t>
+          <t>2025-11-03 06:01:07</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001110710</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004550973</t>
         </is>
       </c>
     </row>
@@ -3191,27 +3191,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AI열풍에 '전자산업 쌀' 풍년… 삼성전기 '뜨끈'</t>
+          <t>‘사모펀드 대주주’ 법안 봇물...먹튀 사라질까</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AI(인공지능) 열풍이 반도체 대형주를 넘어 부품, 기판주로 확산한다. 삼성전기가 수혜주로 부상하고 있다. 테슬라 AI칩 공급계약 이후..</t>
+          <t>국내에서 사모펀드(PE)에 대한 인식은 대체로 좋지 않은 편이다. 지난 1997년 외환위기 직후 론스타 등 외국계 사모펀드들은 대기업 ..</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>이코노미스트</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-11-03 04:03:00</t>
+          <t>2025-11-03 06:00:09</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005272178</t>
+          <t>https://n.news.naver.com/mnews/article/243/0000087371</t>
         </is>
       </c>
     </row>
@@ -3221,25 +3221,115 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>4100선 안착한 코스피, 숨고르기 구간 진입 “수익 방어할 때”</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>코스피가 4100선을 지키며 상승 흐름을 이어갔다. 미국의 금리 인하와 미·중 정상회담 기대감, 반도체 업종의 호실적이 증시를 지탱한 ..</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>디지털타임스</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2025-11-03 05:35:00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/029/0002991013</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>이제 첫 월급 받았는데 노후대비가 웬 말?… "TDF는 달라"</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>#1. 2025년 첫 직장을 구한 A씨(28)는 카드 명세서를 보고 고민에 빠졌다. 사회 진출이 남보다 늦은 만큼 모은 돈은 적은데 씀..</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>머니S</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2025-11-03 05:00:00</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/417/0001110710</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AI열풍에 '전자산업 쌀' 풍년… 삼성전기 '뜨끈'</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AI(인공지능) 열풍이 반도체 대형주를 넘어 부품, 기판주로 확산한다. 삼성전기가 수혜주로 부상하고 있다. 테슬라 AI칩 공급계약 이후..</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>머니투데이</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2025-11-03 04:03:00</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/008/0005272178</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>투심 몰린 파인트리, '렉라자 잡을까' 기대 후보[바이오 다크호스 펀딩]</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>한 주(10월 27일~10월 31일) 제약·바이오 업계에서 주목받은 투자 소식이다. 국내에서는 4곳 이상의 신약개발사가 진행하던 투자라..</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>이데일리</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>2025-11-03 01:00:13</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/018/0006154273</t>
         </is>
